--- a/ConfigSource/Buildings/建筑数值策划表.xlsx
+++ b/ConfigSource/Buildings/建筑数值策划表.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rabad12dbada84e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑家族" sheetId="2" r:id="R7dfd5a7dfc1647ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放置消耗" sheetId="3" r:id="R2cddcd52c92d438d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工消耗" sheetId="4" r:id="R33edf3124c80435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营等级" sheetId="5" r:id="R1ed144020f154692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级消耗" sheetId="6" r:id="R4d7a041d866b4254"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_固定人口" sheetId="7" r:id="R21bf1c04f75d4262"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_库存容量" sheetId="8" r:id="R3e11ca01869f45da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_科技点" sheetId="9" r:id="Re3318e7a431c4ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_住宅" sheetId="10" r:id="R14e9f77f9c3f4a2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_岗位" sheetId="11" r:id="R84a6bfd2a8004b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_生产" sheetId="12" r:id="R183248889eca4fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_捕鱼稀有" sheetId="13" r:id="Rcbffecae161b4fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_市场" sheetId="14" r:id="R0f6648d63c2d456f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_树木" sheetId="15" r:id="R8238ebe676774c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_作物" sheetId="16" r:id="R13f9db0697b1495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_种植消耗" sheetId="17" r:id="R8a0f5f576540457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_收获产出" sheetId="18" r:id="Recd46270b03942e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_自动收获" sheetId="19" r:id="Rdac33ff98092493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视觉样式" sheetId="20" r:id="Rb3f1b78379ac459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="21" r:id="Rd0cafaee1d6a4210"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总检查" sheetId="22" r:id="R586c6ea644654787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R197d0976a4ed4186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑家族" sheetId="2" r:id="Rabbb11d9703149da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放置消耗" sheetId="3" r:id="R685b9d7780f44813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工消耗" sheetId="4" r:id="Rd8c9ef64b63940ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营等级" sheetId="5" r:id="Rd64c9e0b470645f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级消耗" sheetId="6" r:id="R073c750821ad4fc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_固定人口" sheetId="7" r:id="Rb2c3eafaaae74662"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_库存容量" sheetId="8" r:id="Rff0e2b68e2214e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_科技点" sheetId="9" r:id="R798eb83a24c24133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_住宅" sheetId="10" r:id="R15f16088b22f4dbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_岗位" sheetId="11" r:id="R7554ff73eee94b1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_生产" sheetId="12" r:id="R1e2fcb9344794074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_捕鱼稀有" sheetId="13" r:id="Rbace7502330046ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_市场" sheetId="14" r:id="R51eee32654854599"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_树木" sheetId="15" r:id="Ra30d8df8a8764792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_作物" sheetId="16" r:id="R431966c3d6324b21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_种植消耗" sheetId="17" r:id="R93866694ad824282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_收获产出" sheetId="18" r:id="R71dda69e163b4e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_自动收获" sheetId="19" r:id="Rb8aebc210ec041ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视觉样式" sheetId="20" r:id="R1e493ee0a63a402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="21" r:id="R14a213a2744849a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总检查" sheetId="22" r:id="R6203168e19554552"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -987,8 +987,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="ImportDictionary" displayName="ImportDictionary" ref="A4:E29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:E29"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="ImportDictionary" displayName="ImportDictionary" ref="A4:E30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:E30"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="类型"/>
     <x:tableColumn id="2" name="稳定ID/名称"/>
@@ -1372,7 +1372,7 @@
         <x:v>SchemaVersion</x:v>
       </x:c>
       <x:c r="B4" s="47" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="45"/>
       <x:c r="D4" s="45"/>
@@ -2133,7 +2133,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5e24c3be3c34323"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d7068756164bb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2615,7 +2615,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R250ff11b4d2e4493"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R740b5dec848041b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3076,7 +3076,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15c18904e76a48ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R440f6a93825e41c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3412,7 +3412,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1edebdf47ff24b48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde184eef9c7949f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3642,7 +3642,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1ea1f919f524d3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea837da04ea34d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4050,7 +4050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5840fd06a66d433d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64578c4d6f5d44ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5051,7 +5051,7 @@
         <x:v>王宫</x:v>
       </x:c>
       <x:c r="C5" s="73" t="str">
-        <x:v>Housing</x:v>
+        <x:v>市政</x:v>
       </x:c>
       <x:c r="D5" s="75" t="n">
         <x:v>4</x:v>
@@ -5110,7 +5110,7 @@
         <x:v>居民房</x:v>
       </x:c>
       <x:c r="C6" s="74" t="str">
-        <x:v>Housing</x:v>
+        <x:v>人口</x:v>
       </x:c>
       <x:c r="D6" s="76" t="n">
         <x:v>1</x:v>
@@ -5169,7 +5169,7 @@
         <x:v>伐木小屋</x:v>
       </x:c>
       <x:c r="C7" s="74" t="str">
-        <x:v>Production</x:v>
+        <x:v>工业</x:v>
       </x:c>
       <x:c r="D7" s="76" t="n">
         <x:v>1</x:v>
@@ -5228,7 +5228,7 @@
         <x:v>捕鱼小屋</x:v>
       </x:c>
       <x:c r="C8" s="74" t="str">
-        <x:v>Production</x:v>
+        <x:v>农业</x:v>
       </x:c>
       <x:c r="D8" s="76" t="n">
         <x:v>2</x:v>
@@ -5287,7 +5287,7 @@
         <x:v>农田</x:v>
       </x:c>
       <x:c r="C9" s="74" t="str">
-        <x:v>Production</x:v>
+        <x:v>农业</x:v>
       </x:c>
       <x:c r="D9" s="76" t="n">
         <x:v>2</x:v>
@@ -5346,7 +5346,7 @@
         <x:v>市场</x:v>
       </x:c>
       <x:c r="C10" s="74" t="str">
-        <x:v>后勤</x:v>
+        <x:v>经济</x:v>
       </x:c>
       <x:c r="D10" s="76" t="n">
         <x:v>1</x:v>
@@ -5405,7 +5405,7 @@
         <x:v>泥路</x:v>
       </x:c>
       <x:c r="C11" s="74" t="str">
-        <x:v>道路</x:v>
+        <x:v>交通</x:v>
       </x:c>
       <x:c r="D11" s="76" t="n">
         <x:v>1</x:v>
@@ -5464,7 +5464,7 @@
         <x:v>树木</x:v>
       </x:c>
       <x:c r="C12" s="74" t="str">
-        <x:v>美化</x:v>
+        <x:v>装饰</x:v>
       </x:c>
       <x:c r="D12" s="76" t="n">
         <x:v>1</x:v>
@@ -5774,7 +5774,7 @@
   </x:mergeCells>
   <x:dataValidations count="6">
     <x:dataValidation type="list" sqref="C5:C24">
-      <x:formula1>"Housing,Production,Storage,后勤,通用,美化,奇迹,神迹,道路"</x:formula1>
+      <x:formula1>"人口,农业,工业,经济,科研,市政,军事,交通,装饰,奇观"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="F5:F24">
       <x:formula1>"是,否"</x:formula1>
@@ -5794,7 +5794,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc2ecad6c9164c7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9b29f6c53b8476d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6012,7 +6012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb7d24cf234c44e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2274113a98304c3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6075,13 +6075,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B5" s="73" t="str">
-        <x:v>Housing</x:v>
+        <x:v>人口</x:v>
       </x:c>
       <x:c r="C5" s="73" t="str">
-        <x:v>Housing</x:v>
+        <x:v>住宅、人口容量与人口服务</x:v>
       </x:c>
       <x:c r="D5" s="73" t="str">
-        <x:v>BuildingCategory.Housing</x:v>
+        <x:v>BuildingCategory.人口</x:v>
       </x:c>
       <x:c r="E5" s="73" t="str">
         <x:v>是</x:v>
@@ -6092,13 +6092,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B6" s="74" t="str">
-        <x:v>Production</x:v>
+        <x:v>农业</x:v>
       </x:c>
       <x:c r="C6" s="74" t="str">
-        <x:v>Production</x:v>
+        <x:v>种植、养殖、捕鱼与食物获取</x:v>
       </x:c>
       <x:c r="D6" s="74" t="str">
-        <x:v>BuildingCategory.Production</x:v>
+        <x:v>BuildingCategory.农业</x:v>
       </x:c>
       <x:c r="E6" s="74" t="str">
         <x:v>是</x:v>
@@ -6109,13 +6109,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B7" s="74" t="str">
-        <x:v>Storage</x:v>
+        <x:v>工业</x:v>
       </x:c>
       <x:c r="C7" s="74" t="str">
-        <x:v>Storage</x:v>
+        <x:v>资源采集、加工与制造</x:v>
       </x:c>
       <x:c r="D7" s="74" t="str">
-        <x:v>BuildingCategory.Storage</x:v>
+        <x:v>BuildingCategory.工业</x:v>
       </x:c>
       <x:c r="E7" s="74" t="str">
         <x:v>是</x:v>
@@ -6126,13 +6126,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B8" s="74" t="str">
-        <x:v>后勤</x:v>
+        <x:v>经济</x:v>
       </x:c>
       <x:c r="C8" s="74" t="str">
-        <x:v>后勤</x:v>
+        <x:v>市场、贸易与财政</x:v>
       </x:c>
       <x:c r="D8" s="74" t="str">
-        <x:v>BuildingCategory.后勤</x:v>
+        <x:v>BuildingCategory.经济</x:v>
       </x:c>
       <x:c r="E8" s="74" t="str">
         <x:v>是</x:v>
@@ -6143,13 +6143,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B9" s="74" t="str">
-        <x:v>通用</x:v>
+        <x:v>科研</x:v>
       </x:c>
       <x:c r="C9" s="74" t="str">
-        <x:v>通用</x:v>
+        <x:v>研究与科技产出</x:v>
       </x:c>
       <x:c r="D9" s="74" t="str">
-        <x:v>BuildingCategory.通用</x:v>
+        <x:v>BuildingCategory.科研</x:v>
       </x:c>
       <x:c r="E9" s="74" t="str">
         <x:v>是</x:v>
@@ -6160,13 +6160,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B10" s="74" t="str">
-        <x:v>美化</x:v>
+        <x:v>市政</x:v>
       </x:c>
       <x:c r="C10" s="74" t="str">
-        <x:v>美化</x:v>
+        <x:v>治理、公共服务与城市核心</x:v>
       </x:c>
       <x:c r="D10" s="74" t="str">
-        <x:v>BuildingCategory.美化</x:v>
+        <x:v>BuildingCategory.市政</x:v>
       </x:c>
       <x:c r="E10" s="74" t="str">
         <x:v>是</x:v>
@@ -6177,13 +6177,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B11" s="74" t="str">
-        <x:v>奇迹</x:v>
+        <x:v>军事</x:v>
       </x:c>
       <x:c r="C11" s="74" t="str">
-        <x:v>奇迹</x:v>
+        <x:v>防御、驻军与训练</x:v>
       </x:c>
       <x:c r="D11" s="74" t="str">
-        <x:v>BuildingCategory.奇迹</x:v>
+        <x:v>BuildingCategory.军事</x:v>
       </x:c>
       <x:c r="E11" s="74" t="str">
         <x:v>是</x:v>
@@ -6194,13 +6194,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B12" s="74" t="str">
-        <x:v>神迹</x:v>
+        <x:v>交通</x:v>
       </x:c>
       <x:c r="C12" s="74" t="str">
-        <x:v>神迹</x:v>
+        <x:v>道路、运输与通行设施</x:v>
       </x:c>
       <x:c r="D12" s="74" t="str">
-        <x:v>BuildingCategory.神迹</x:v>
+        <x:v>BuildingCategory.交通</x:v>
       </x:c>
       <x:c r="E12" s="74" t="str">
         <x:v>是</x:v>
@@ -6211,13 +6211,13 @@
         <x:v>Category</x:v>
       </x:c>
       <x:c r="B13" s="74" t="str">
-        <x:v>道路</x:v>
+        <x:v>装饰</x:v>
       </x:c>
       <x:c r="C13" s="74" t="str">
-        <x:v>道路</x:v>
+        <x:v>景观与非核心装饰</x:v>
       </x:c>
       <x:c r="D13" s="74" t="str">
-        <x:v>BuildingCategory.道路</x:v>
+        <x:v>BuildingCategory.装饰</x:v>
       </x:c>
       <x:c r="E13" s="74" t="str">
         <x:v>是</x:v>
@@ -6225,16 +6225,16 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="74" t="str">
-        <x:v>Item</x:v>
+        <x:v>Category</x:v>
       </x:c>
       <x:c r="B14" s="74" t="str">
-        <x:v>金币</x:v>
+        <x:v>奇观</x:v>
       </x:c>
       <x:c r="C14" s="74" t="str">
-        <x:v>金币</x:v>
+        <x:v>唯一性或里程碑大型建筑</x:v>
       </x:c>
       <x:c r="D14" s="74" t="str">
-        <x:v>ItemDefinition.ItemId</x:v>
+        <x:v>BuildingCategory.奇观</x:v>
       </x:c>
       <x:c r="E14" s="74" t="str">
         <x:v>是</x:v>
@@ -6245,10 +6245,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B15" s="74" t="str">
-        <x:v>泥土</x:v>
+        <x:v>金币</x:v>
       </x:c>
       <x:c r="C15" s="74" t="str">
-        <x:v>泥土</x:v>
+        <x:v>金币</x:v>
       </x:c>
       <x:c r="D15" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6262,10 +6262,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B16" s="74" t="str">
-        <x:v>石头</x:v>
+        <x:v>泥土</x:v>
       </x:c>
       <x:c r="C16" s="74" t="str">
-        <x:v>石头</x:v>
+        <x:v>泥土</x:v>
       </x:c>
       <x:c r="D16" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6279,10 +6279,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B17" s="74" t="str">
-        <x:v>原木</x:v>
+        <x:v>石头</x:v>
       </x:c>
       <x:c r="C17" s="74" t="str">
-        <x:v>原木</x:v>
+        <x:v>石头</x:v>
       </x:c>
       <x:c r="D17" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6296,10 +6296,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B18" s="74" t="str">
-        <x:v>木头</x:v>
+        <x:v>原木</x:v>
       </x:c>
       <x:c r="C18" s="74" t="str">
-        <x:v>木头</x:v>
+        <x:v>原木</x:v>
       </x:c>
       <x:c r="D18" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6313,10 +6313,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B19" s="74" t="str">
-        <x:v>树苗</x:v>
+        <x:v>木头</x:v>
       </x:c>
       <x:c r="C19" s="74" t="str">
-        <x:v>树苗</x:v>
+        <x:v>木头</x:v>
       </x:c>
       <x:c r="D19" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6330,10 +6330,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B20" s="74" t="str">
-        <x:v>蔬菜</x:v>
+        <x:v>树苗</x:v>
       </x:c>
       <x:c r="C20" s="74" t="str">
-        <x:v>蔬菜</x:v>
+        <x:v>树苗</x:v>
       </x:c>
       <x:c r="D20" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6347,10 +6347,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B21" s="74" t="str">
-        <x:v>鱼</x:v>
+        <x:v>蔬菜</x:v>
       </x:c>
       <x:c r="C21" s="74" t="str">
-        <x:v>鱼</x:v>
+        <x:v>蔬菜</x:v>
       </x:c>
       <x:c r="D21" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6364,10 +6364,10 @@
         <x:v>Item</x:v>
       </x:c>
       <x:c r="B22" s="74" t="str">
-        <x:v>黄金鱼</x:v>
+        <x:v>鱼</x:v>
       </x:c>
       <x:c r="C22" s="74" t="str">
-        <x:v>黄金鱼</x:v>
+        <x:v>鱼</x:v>
       </x:c>
       <x:c r="D22" s="74" t="str">
         <x:v>ItemDefinition.ItemId</x:v>
@@ -6378,16 +6378,16 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="74" t="str">
-        <x:v>Condition</x:v>
+        <x:v>Item</x:v>
       </x:c>
       <x:c r="B23" s="74" t="str">
-        <x:v>none</x:v>
+        <x:v>黄金鱼</x:v>
       </x:c>
       <x:c r="C23" s="74" t="str">
-        <x:v>无升级条件</x:v>
+        <x:v>黄金鱼</x:v>
       </x:c>
       <x:c r="D23" s="74" t="str">
-        <x:v>null</x:v>
+        <x:v>ItemDefinition.ItemId</x:v>
       </x:c>
       <x:c r="E23" s="74" t="str">
         <x:v>是</x:v>
@@ -6398,13 +6398,13 @@
         <x:v>Condition</x:v>
       </x:c>
       <x:c r="B24" s="74" t="str">
-        <x:v>keep</x:v>
+        <x:v>none</x:v>
       </x:c>
       <x:c r="C24" s="74" t="str">
-        <x:v>保留现有条件（仅现有等级）</x:v>
+        <x:v>无升级条件</x:v>
       </x:c>
       <x:c r="D24" s="74" t="str">
-        <x:v>现有 GameCondition</x:v>
+        <x:v>null</x:v>
       </x:c>
       <x:c r="E24" s="74" t="str">
         <x:v>是</x:v>
@@ -6415,13 +6415,13 @@
         <x:v>Condition</x:v>
       </x:c>
       <x:c r="B25" s="74" t="str">
-        <x:v>technology.TN_3_1_启蒙</x:v>
+        <x:v>keep</x:v>
       </x:c>
       <x:c r="C25" s="74" t="str">
-        <x:v>启蒙科技解锁</x:v>
+        <x:v>保留现有条件（仅现有等级）</x:v>
       </x:c>
       <x:c r="D25" s="74" t="str">
-        <x:v>GameCondition_TechnologyUnlocked</x:v>
+        <x:v>现有 GameCondition</x:v>
       </x:c>
       <x:c r="E25" s="74" t="str">
         <x:v>是</x:v>
@@ -6429,19 +6429,19 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="74" t="str">
-        <x:v>Presentation</x:v>
+        <x:v>Condition</x:v>
       </x:c>
       <x:c r="B26" s="74" t="str">
-        <x:v>StyleId</x:v>
+        <x:v>technology.TN_3_1_启蒙</x:v>
       </x:c>
       <x:c r="C26" s="74" t="str">
-        <x:v>视觉变体，不产生新家族</x:v>
+        <x:v>启蒙科技解锁</x:v>
       </x:c>
       <x:c r="D26" s="74" t="str">
-        <x:v>BuildingPresentationDefinition</x:v>
+        <x:v>GameCondition_TechnologyUnlocked</x:v>
       </x:c>
       <x:c r="E26" s="74" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6449,13 +6449,13 @@
         <x:v>Presentation</x:v>
       </x:c>
       <x:c r="B27" s="74" t="str">
-        <x:v>Icon/View Path</x:v>
+        <x:v>StyleId</x:v>
       </x:c>
       <x:c r="C27" s="74" t="str">
-        <x:v>美术回填清单</x:v>
+        <x:v>视觉变体，不产生新家族</x:v>
       </x:c>
       <x:c r="D27" s="74" t="str">
-        <x:v>Unity 对象引用</x:v>
+        <x:v>BuildingPresentationDefinition</x:v>
       </x:c>
       <x:c r="E27" s="74" t="str">
         <x:v>否</x:v>
@@ -6463,16 +6463,16 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="74" t="str">
-        <x:v>Structure</x:v>
+        <x:v>Presentation</x:v>
       </x:c>
       <x:c r="B28" s="74" t="str">
-        <x:v>ModuleSet</x:v>
+        <x:v>Icon/View Path</x:v>
       </x:c>
       <x:c r="C28" s="74" t="str">
-        <x:v>模块类型和启用状态</x:v>
+        <x:v>美术回填清单</x:v>
       </x:c>
       <x:c r="D28" s="74" t="str">
-        <x:v>BuildingModuleSetDefinition</x:v>
+        <x:v>Unity 对象引用</x:v>
       </x:c>
       <x:c r="E28" s="74" t="str">
         <x:v>否</x:v>
@@ -6483,15 +6483,32 @@
         <x:v>Structure</x:v>
       </x:c>
       <x:c r="B29" s="74" t="str">
+        <x:v>ModuleSet</x:v>
+      </x:c>
+      <x:c r="C29" s="74" t="str">
+        <x:v>模块类型和启用状态</x:v>
+      </x:c>
+      <x:c r="D29" s="74" t="str">
+        <x:v>BuildingModuleSetDefinition</x:v>
+      </x:c>
+      <x:c r="E29" s="74" t="str">
+        <x:v>否</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="74" t="str">
+        <x:v>Structure</x:v>
+      </x:c>
+      <x:c r="B30" s="74" t="str">
         <x:v>Runtime Prefab</x:v>
       </x:c>
-      <x:c r="C29" s="74" t="str">
+      <x:c r="C30" s="74" t="str">
         <x:v>组件与层级结构</x:v>
       </x:c>
-      <x:c r="D29" s="74" t="str">
+      <x:c r="D30" s="74" t="str">
         <x:v>Prefab</x:v>
       </x:c>
-      <x:c r="E29" s="74" t="str">
+      <x:c r="E30" s="74" t="str">
         <x:v>否</x:v>
       </x:c>
     </x:row>
@@ -6502,7 +6519,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R117a779344ed48e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8418d5735ae4ebf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6642,17 +6659,17 @@
       </x:c>
       <x:c r="B9" s="81" t="n">
         <x:f>'说明'!B4</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C9" s="76" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="79" t="str">
         <x:f>IF(B9=C9,"通过","待检查")</x:f>
         <x:v>通过</x:v>
       </x:c>
       <x:c r="E9" s="74" t="str">
-        <x:v>必须与 Unity 导表器一致</x:v>
+        <x:v>分类枚举已迁移为十类；必须与 Unity 导表器一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6667,7 +6684,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c682ca5fa594317"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f3e326638bf462d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6893,7 +6910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbf5007f20ab4945"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c326d8128474c3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7136,7 +7153,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18a3c2b2e4294ac9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12b6191568f341db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7509,7 +7526,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R591b504383c043d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ef2a3b3a1ea45a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7732,7 +7749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b8348f256574201"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8398a891640043de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7956,7 +7973,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7752c4537984bf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac36f5286ee4d22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8180,7 +8197,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42db289af2014bfb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17bfa8e5f5244973"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8404,7 +8421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b88b8bcab7a4f9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R915513cc7e914fd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ConfigSource/Buildings/建筑数值策划表.xlsx
+++ b/ConfigSource/Buildings/建筑数值策划表.xlsx
@@ -2,34 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R158c1c17cce449b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑家族" sheetId="2" r:id="Rc2690a4330de42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放置消耗" sheetId="3" r:id="R73fbe76105a24904"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工消耗" sheetId="4" r:id="R6bcaa513d69f4e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营等级" sheetId="5" r:id="Rce20adcc6ed34f67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级消耗" sheetId="6" r:id="Rff35394557d34f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_固定人口" sheetId="7" r:id="Rdfc87841b92349a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_库存容量" sheetId="8" r:id="Rfbe7c6bd95744ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_科技点" sheetId="9" r:id="Rbd0a4ac5a5b34252"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_住宅" sheetId="10" r:id="R1e0f9f8940d94e52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_岗位" sheetId="11" r:id="Rfa9a482e82f34229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_生产" sheetId="12" r:id="R3aab584ae89648f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_捕鱼稀有" sheetId="13" r:id="R4fd0ee5244af4eb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_仓库" sheetId="14" r:id="R3c1fb0c7c9e746f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_市场" sheetId="15" r:id="R2d2c90e3b80344af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_树木" sheetId="16" r:id="R913a562d4fd54879"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_范围效果" sheetId="17" r:id="R0dbf6c075fd74885"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_作物" sheetId="18" r:id="R3243ab7fea25417e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_种植消耗" sheetId="19" r:id="R2a95f0013821422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_收获产出" sheetId="20" r:id="Ra2f7a28a4f6843a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_自动收获" sheetId="21" r:id="Radf554d21e92439d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视觉样式" sheetId="22" r:id="R71c891255ace4b66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="23" r:id="Rcfd33b659cc849cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总检查" sheetId="24" r:id="Rf2627bcd5ea3466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工产出" sheetId="25" r:id="Rd54e065bb9b34095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_维护费" sheetId="26" r:id="R499f164666f641bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局生产Buff" sheetId="27" r:id="R24cf944cecc541f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_运营经验" sheetId="28" r:id="R07d404b8dba34b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rb4adb776360d4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑家族" sheetId="2" r:id="Rc7871536722b48ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放置消耗" sheetId="3" r:id="R7214b6bef49049e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工消耗" sheetId="4" r:id="R9fb411d168494f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营等级" sheetId="5" r:id="Ra6f97a1dc2084b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级消耗" sheetId="6" r:id="Rca91b372040d4066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_固定人口" sheetId="7" r:id="R1429843eae524a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_库存容量" sheetId="8" r:id="R6a51c408e21d4e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_科技点" sheetId="9" r:id="Ra84d01f896ba4799"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_住宅" sheetId="10" r:id="R7afa443cff83447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_岗位" sheetId="11" r:id="R9097a1e7c409491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_生产" sheetId="12" r:id="R5dd6d7e57ff04c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_捕鱼稀有" sheetId="13" r:id="Rf30c877fc22741bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_仓库" sheetId="14" r:id="R8e9ce252264949a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_市场" sheetId="15" r:id="R0d802827293f4863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_树木" sheetId="16" r:id="R5f47d26e37794698"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_范围效果" sheetId="17" r:id="Rba4bf5992c3249aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_作物" sheetId="18" r:id="Re63d5e45943d4800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_种植消耗" sheetId="19" r:id="R51969da14f174e70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_收获产出" sheetId="20" r:id="R2da33eb1006944a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_自动收获" sheetId="21" r:id="Rd7ba4fef24cc4e61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视觉样式" sheetId="22" r:id="R548c4d1efb0e4614"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="23" r:id="R83985afb69554fec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总检查" sheetId="24" r:id="R561f9a95dba3472e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工产出" sheetId="25" r:id="R5d35689fd8a94704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_维护费" sheetId="26" r:id="Re8124296c1934666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局生产Buff" sheetId="27" r:id="R79745b744f8645cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_运营经验" sheetId="28" r:id="R2304328841334be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局库存Buff" sheetId="29" r:id="Rbfeab2baf1974594"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,7 +47,7 @@
     <x:numFmt numFmtId="166" formatCode="0.0%"/>
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="30">
+  <x:fonts count="31">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -210,8 +211,13 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="63">
+  <x:fills count="69">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -523,8 +529,38 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF203864"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="28">
+  <x:borders count="30">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -790,6 +826,34 @@
         <x:color rgb="FFB4C6E7"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF9FBAD0"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D9D9"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="50">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -941,7 +1005,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="159">
+  <x:cellXfs count="186">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -1289,6 +1353,51 @@
     <x:xf numFmtId="0" fontId="0" fillId="62" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="62" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="62" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="63" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="63" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="63" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="63" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="64" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="64" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="65" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="28" fillId="66" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="67" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="67" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="67" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="67" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="68" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="68" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="68" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="68" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="30" fillId="68" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -2173,7 +2282,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="29" t="n">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="3" t="n"/>
       <x:c r="D4" s="3" t="n"/>
@@ -2272,7 +2381,7 @@
         <x:v>Excel 导入</x:v>
       </x:c>
       <x:c r="B11" s="32" t="str">
-        <x:v>建筑公共数值、蓝图自动条件、地形覆盖要求、放置/施工消耗与产出、升级、岗位/维护费/运营经验、等级配置、全局生产 Buff、仓库/市场/树木/医疗/治安范围效果/作物模块默认值</x:v>
+        <x:v>建筑公共数值、蓝图自动条件、地形覆盖要求、放置/施工消耗与产出、升级、岗位/维护费/运营经验、等级配置、居民饮食、建筑提供的库存槽位类型与数量、全局生产 Buff、仓库/市场/树木/范围效果/作物模块默认值</x:v>
       </x:c>
       <x:c r="C11" s="43" t="n"/>
       <x:c r="D11" s="43" t="n"/>
@@ -2325,10 +2434,10 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="34" t="str">
-        <x:v>条件</x:v>
+        <x:v>槽位类型</x:v>
       </x:c>
       <x:c r="B15" s="35" t="str">
-        <x:v>蓝图/全局 Buff 条件支持 none 或 technology.&lt;TechnologyId&gt;；升级条件额外支持 keep</x:v>
+        <x:v>建筑表只选择 InventorySlotType 和数量；槽位基础损耗、物品组修正及自动存放优先级由库存系统数值表管理</x:v>
       </x:c>
       <x:c r="C15" s="45" t="n"/>
       <x:c r="D15" s="45" t="n"/>
@@ -2462,6 +2571,11 @@
     <x:col min="7" max="8" width="15" style="42" customWidth="1"/>
     <x:col min="9" max="9" width="11" style="42" customWidth="1"/>
     <x:col min="10" max="11" width="18" style="42" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="42" customFormat="1" ht="30" customHeight="1">
@@ -2472,10 +2586,8 @@
       </x:c>
     </x:row>
     <x:row r="2" s="42" customFormat="1" ht="38" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">对应 ResidentialHousingLevelConfiguration。食物按当前人口每回合消耗，满人口食物/回合是公式提示，不参与导入。</x:t>
-        </x:is>
+      <x:c r="A2" s="2" t="str">
+        <x:v>对应 ResidentialHousingLevelConfiguration。人口、食物组、饮食选择和生活质量均属于住宅建筑配置；Item/ItemGroup 定义仍由库存系统数值表提供。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2547,6 +2659,21 @@
           <x:t xml:space="preserve">校验</x:t>
         </x:is>
       </x:c>
+      <x:c r="L4" s="163" t="str">
+        <x:v>FoodGroupId</x:v>
+      </x:c>
+      <x:c r="M4" s="163" t="str">
+        <x:v>选择策略</x:v>
+      </x:c>
+      <x:c r="N4" s="163" t="str">
+        <x:v>目标饮食种类</x:v>
+      </x:c>
+      <x:c r="O4" s="163" t="str">
+        <x:v>生活质量变化/回合</x:v>
+      </x:c>
+      <x:c r="P4" s="163" t="str">
+        <x:v>高质量增长阈值</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="inlineStr">
@@ -2590,6 +2717,21 @@
         <x:f>IF(D5&lt;C5,"错误：人口上限","通过")</x:f>
         <x:v>通过</x:v>
       </x:c>
+      <x:c r="L5" s="165" t="str">
+        <x:v>food.vegetable</x:v>
+      </x:c>
+      <x:c r="M5" s="165" t="str">
+        <x:v>PreferVariety</x:v>
+      </x:c>
+      <x:c r="N5" s="165" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O5" s="165" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P5" s="165" t="n">
+        <x:v>80</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="inlineStr">
@@ -2633,6 +2775,21 @@
         <x:f>IF(D6&lt;C6,"错误：人口上限","通过")</x:f>
         <x:v>通过</x:v>
       </x:c>
+      <x:c r="L6" s="165" t="str">
+        <x:v>food.vegetable</x:v>
+      </x:c>
+      <x:c r="M6" s="165" t="str">
+        <x:v>PreferVariety</x:v>
+      </x:c>
+      <x:c r="N6" s="165" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O6" s="165" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P6" s="165" t="n">
+        <x:v>80</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="inlineStr">
@@ -2676,6 +2833,21 @@
         <x:f>IF(D7&lt;C7,"错误：人口上限","通过")</x:f>
         <x:v>通过</x:v>
       </x:c>
+      <x:c r="L7" s="165" t="str">
+        <x:v>food.vegetable</x:v>
+      </x:c>
+      <x:c r="M7" s="165" t="str">
+        <x:v>PreferVariety</x:v>
+      </x:c>
+      <x:c r="N7" s="165" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O7" s="165" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P7" s="165" t="n">
+        <x:v>80</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="inlineStr">
@@ -2718,6 +2890,21 @@
       <x:c r="K8" s="14" t="str">
         <x:f>IF(D8&lt;C8,"错误：人口上限","通过")</x:f>
         <x:v>通过</x:v>
+      </x:c>
+      <x:c r="L8" s="165" t="str">
+        <x:v>food.vegetable</x:v>
+      </x:c>
+      <x:c r="M8" s="165" t="str">
+        <x:v>PreferVariety</x:v>
+      </x:c>
+      <x:c r="N8" s="165" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O8" s="165" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="P8" s="165" t="n">
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2732,6 +2919,11 @@
       <x:c r="I9" s="15" t="n"/>
       <x:c r="J9" s="15" t="n"/>
       <x:c r="K9" s="3" t="n"/>
+      <x:c r="L9" s="165"/>
+      <x:c r="M9" s="165"/>
+      <x:c r="N9" s="165"/>
+      <x:c r="O9" s="165"/>
+      <x:c r="P9" s="165"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="n"/>
@@ -2745,6 +2937,11 @@
       <x:c r="I10" s="15" t="n"/>
       <x:c r="J10" s="15" t="n"/>
       <x:c r="K10" s="3" t="n"/>
+      <x:c r="L10" s="165"/>
+      <x:c r="M10" s="165"/>
+      <x:c r="N10" s="165"/>
+      <x:c r="O10" s="165"/>
+      <x:c r="P10" s="165"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="n"/>
@@ -2758,6 +2955,11 @@
       <x:c r="I11" s="15" t="n"/>
       <x:c r="J11" s="15" t="n"/>
       <x:c r="K11" s="3" t="n"/>
+      <x:c r="L11" s="165"/>
+      <x:c r="M11" s="165"/>
+      <x:c r="N11" s="165"/>
+      <x:c r="O11" s="165"/>
+      <x:c r="P11" s="165"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="3" t="n"/>
@@ -2771,6 +2973,11 @@
       <x:c r="I12" s="15" t="n"/>
       <x:c r="J12" s="15" t="n"/>
       <x:c r="K12" s="3" t="n"/>
+      <x:c r="L12" s="165"/>
+      <x:c r="M12" s="165"/>
+      <x:c r="N12" s="165"/>
+      <x:c r="O12" s="165"/>
+      <x:c r="P12" s="165"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="3" t="n"/>
@@ -2784,6 +2991,11 @@
       <x:c r="I13" s="15" t="n"/>
       <x:c r="J13" s="15" t="n"/>
       <x:c r="K13" s="3" t="n"/>
+      <x:c r="L13" s="165"/>
+      <x:c r="M13" s="165"/>
+      <x:c r="N13" s="165"/>
+      <x:c r="O13" s="165"/>
+      <x:c r="P13" s="165"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="3" t="n"/>
@@ -2797,6 +3009,11 @@
       <x:c r="I14" s="15" t="n"/>
       <x:c r="J14" s="15" t="n"/>
       <x:c r="K14" s="3" t="n"/>
+      <x:c r="L14" s="165"/>
+      <x:c r="M14" s="165"/>
+      <x:c r="N14" s="165"/>
+      <x:c r="O14" s="165"/>
+      <x:c r="P14" s="165"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="3" t="n"/>
@@ -2810,6 +3027,11 @@
       <x:c r="I15" s="15" t="n"/>
       <x:c r="J15" s="15" t="n"/>
       <x:c r="K15" s="3" t="n"/>
+      <x:c r="L15" s="165"/>
+      <x:c r="M15" s="165"/>
+      <x:c r="N15" s="165"/>
+      <x:c r="O15" s="165"/>
+      <x:c r="P15" s="165"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="3" t="n"/>
@@ -2823,6 +3045,11 @@
       <x:c r="I16" s="15" t="n"/>
       <x:c r="J16" s="15" t="n"/>
       <x:c r="K16" s="3" t="n"/>
+      <x:c r="L16" s="165"/>
+      <x:c r="M16" s="165"/>
+      <x:c r="N16" s="165"/>
+      <x:c r="O16" s="165"/>
+      <x:c r="P16" s="165"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="3" t="n"/>
@@ -2836,6 +3063,11 @@
       <x:c r="I17" s="15" t="n"/>
       <x:c r="J17" s="15" t="n"/>
       <x:c r="K17" s="3" t="n"/>
+      <x:c r="L17" s="165"/>
+      <x:c r="M17" s="165"/>
+      <x:c r="N17" s="165"/>
+      <x:c r="O17" s="165"/>
+      <x:c r="P17" s="165"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="3" t="n"/>
@@ -2849,6 +3081,11 @@
       <x:c r="I18" s="15" t="n"/>
       <x:c r="J18" s="15" t="n"/>
       <x:c r="K18" s="3" t="n"/>
+      <x:c r="L18" s="165"/>
+      <x:c r="M18" s="165"/>
+      <x:c r="N18" s="165"/>
+      <x:c r="O18" s="165"/>
+      <x:c r="P18" s="165"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="3" t="n"/>
@@ -2862,6 +3099,11 @@
       <x:c r="I19" s="15" t="n"/>
       <x:c r="J19" s="15" t="n"/>
       <x:c r="K19" s="3" t="n"/>
+      <x:c r="L19" s="165"/>
+      <x:c r="M19" s="165"/>
+      <x:c r="N19" s="165"/>
+      <x:c r="O19" s="165"/>
+      <x:c r="P19" s="165"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="3" t="n"/>
@@ -2875,6 +3117,11 @@
       <x:c r="I20" s="15" t="n"/>
       <x:c r="J20" s="15" t="n"/>
       <x:c r="K20" s="3" t="n"/>
+      <x:c r="L20" s="165"/>
+      <x:c r="M20" s="165"/>
+      <x:c r="N20" s="165"/>
+      <x:c r="O20" s="165"/>
+      <x:c r="P20" s="165"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="3" t="n"/>
@@ -2888,6 +3135,11 @@
       <x:c r="I21" s="15" t="n"/>
       <x:c r="J21" s="15" t="n"/>
       <x:c r="K21" s="3" t="n"/>
+      <x:c r="L21" s="165"/>
+      <x:c r="M21" s="165"/>
+      <x:c r="N21" s="165"/>
+      <x:c r="O21" s="165"/>
+      <x:c r="P21" s="165"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="3" t="n"/>
@@ -2901,6 +3153,11 @@
       <x:c r="I22" s="15" t="n"/>
       <x:c r="J22" s="15" t="n"/>
       <x:c r="K22" s="3" t="n"/>
+      <x:c r="L22" s="165"/>
+      <x:c r="M22" s="165"/>
+      <x:c r="N22" s="165"/>
+      <x:c r="O22" s="165"/>
+      <x:c r="P22" s="165"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="3" t="n"/>
@@ -2914,6 +3171,11 @@
       <x:c r="I23" s="15" t="n"/>
       <x:c r="J23" s="15" t="n"/>
       <x:c r="K23" s="3" t="n"/>
+      <x:c r="L23" s="165"/>
+      <x:c r="M23" s="165"/>
+      <x:c r="N23" s="165"/>
+      <x:c r="O23" s="165"/>
+      <x:c r="P23" s="165"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="3" t="n"/>
@@ -2927,6 +3189,11 @@
       <x:c r="I24" s="15" t="n"/>
       <x:c r="J24" s="15" t="n"/>
       <x:c r="K24" s="3" t="n"/>
+      <x:c r="L24" s="165"/>
+      <x:c r="M24" s="165"/>
+      <x:c r="N24" s="165"/>
+      <x:c r="O24" s="165"/>
+      <x:c r="P24" s="165"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2944,17 +3211,20 @@
       <x:formula>NOT(ISERROR(SEARCH("错误",K5)))</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A5:A24">
       <x:formula1>"building.player_home,building.residential_house,building.lumber_cabin,building.fishing_hut,building.farm_field,building.market,building.warehouse,building.road,building.tree"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="E5:E24 H5:H24">
       <x:formula1>"金币,泥土,石头,原木,木板,树苗,蔬菜,鱼,黄金鱼"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="M5:M24">
+      <x:formula1>"PreferSoonToSpoil,PreferVariety,PreferQuality,PreferLowestValue"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1a55f94c5894394"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7864dc9d7ed48b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3751,7 +4021,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R516b3cf7439e48cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb24d3efd470548c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4570,7 +4840,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R384e72c3bad040d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc3f89b25b5d4462"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4929,7 +5199,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5627a156515b4766"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25e95b44002d47e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4949,6 +5219,8 @@
     <x:col min="9" max="10" width="15" style="42" customWidth="1"/>
     <x:col min="11" max="11" width="13" style="42" customWidth="1"/>
     <x:col min="12" max="13" width="22" style="42" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="42" customFormat="1" ht="30" customHeight="1">
@@ -4959,10 +5231,8 @@
       </x:c>
     </x:row>
     <x:row r="2" s="42" customFormat="1" ht="38" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">对应 WarehouseLevelConfiguration / BM_仓库运营。基础库存格只在达到容量所需工人时生效；维护失败会阻止经验并降低本建筑岗位吸引力。</x:t>
-        </x:is>
+      <x:c r="A2" s="2" t="str">
+        <x:v>对应 WarehouseLevelConfiguration / BM_仓库运营。基础槽位始终存在；工人不足或维护失败只产生运行时损耗倍率。建筑表配置基础/奖励槽位类型，库存系统解析该类型的固定规则。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4991,10 +5261,8 @@
           <x:t xml:space="preserve">Level</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">容量所需工人</x:t>
-        </x:is>
+      <x:c r="C4" s="5" t="str">
+        <x:v>正常仓储所需工人</x:v>
       </x:c>
       <x:c r="D4" s="5" t="inlineStr">
         <x:is>
@@ -5045,6 +5313,12 @@
         <x:is>
           <x:t xml:space="preserve">校验</x:t>
         </x:is>
+      </x:c>
+      <x:c r="N4" s="163" t="str">
+        <x:v>基础槽位类型</x:v>
+      </x:c>
+      <x:c r="O4" s="163" t="str">
+        <x:v>奖励槽位类型</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -5092,6 +5366,12 @@
         <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A5,等级_岗位!$B$5:$B$24,B5)=0,"错误：缺少岗位",IF(MAX(C5,G5,J5)&gt;SUMIFS(等级_岗位!$C$5:$C$24,等级_岗位!$A$5:$A$24,A5,等级_岗位!$B$5:$B$24,B5),"错误：阈值超上限","通过"))</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
+      <x:c r="N5" s="165" t="str">
+        <x:v>BasicWarehouse</x:v>
+      </x:c>
+      <x:c r="O5" s="165" t="str">
+        <x:v>BasicWarehouse</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="inlineStr">
@@ -5138,6 +5418,12 @@
         <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A6,等级_岗位!$B$5:$B$24,B6)=0,"错误：缺少岗位",IF(MAX(C6,G6,J6)&gt;SUMIFS(等级_岗位!$C$5:$C$24,等级_岗位!$A$5:$A$24,A6,等级_岗位!$B$5:$B$24,B6),"错误：阈值超上限","通过"))</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
+      <x:c r="N6" s="165" t="str">
+        <x:v>Warehouse</x:v>
+      </x:c>
+      <x:c r="O6" s="165" t="str">
+        <x:v>Warehouse</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="inlineStr">
@@ -5183,6 +5469,12 @@
       <x:c r="M7" s="14" t="e">
         <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A7,等级_岗位!$B$5:$B$24,B7)=0,"错误：缺少岗位",IF(MAX(C7,G7,J7)&gt;SUMIFS(等级_岗位!$C$5:$C$24,等级_岗位!$A$5:$A$24,A7,等级_岗位!$B$5:$B$24,B7),"错误：阈值超上限","通过"))</x:f>
         <x:v>#NAME?</x:v>
+      </x:c>
+      <x:c r="N7" s="165" t="str">
+        <x:v>AdvancedWarehouse</x:v>
+      </x:c>
+      <x:c r="O7" s="165" t="str">
+        <x:v>AdvancedWarehouse</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5199,6 +5491,8 @@
       <x:c r="K8" s="15" t="n"/>
       <x:c r="L8" s="15" t="n"/>
       <x:c r="M8" s="3" t="n"/>
+      <x:c r="N8" s="165"/>
+      <x:c r="O8" s="165"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="n"/>
@@ -5214,6 +5508,8 @@
       <x:c r="K9" s="15" t="n"/>
       <x:c r="L9" s="15" t="n"/>
       <x:c r="M9" s="3" t="n"/>
+      <x:c r="N9" s="165"/>
+      <x:c r="O9" s="165"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="n"/>
@@ -5229,6 +5525,8 @@
       <x:c r="K10" s="15" t="n"/>
       <x:c r="L10" s="15" t="n"/>
       <x:c r="M10" s="3" t="n"/>
+      <x:c r="N10" s="165"/>
+      <x:c r="O10" s="165"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="n"/>
@@ -5244,6 +5542,8 @@
       <x:c r="K11" s="15" t="n"/>
       <x:c r="L11" s="15" t="n"/>
       <x:c r="M11" s="3" t="n"/>
+      <x:c r="N11" s="165"/>
+      <x:c r="O11" s="165"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="3" t="n"/>
@@ -5259,6 +5559,8 @@
       <x:c r="K12" s="15" t="n"/>
       <x:c r="L12" s="15" t="n"/>
       <x:c r="M12" s="3" t="n"/>
+      <x:c r="N12" s="165"/>
+      <x:c r="O12" s="165"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="3" t="n"/>
@@ -5274,6 +5576,8 @@
       <x:c r="K13" s="15" t="n"/>
       <x:c r="L13" s="15" t="n"/>
       <x:c r="M13" s="3" t="n"/>
+      <x:c r="N13" s="165"/>
+      <x:c r="O13" s="165"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="3" t="n"/>
@@ -5289,6 +5593,8 @@
       <x:c r="K14" s="15" t="n"/>
       <x:c r="L14" s="15" t="n"/>
       <x:c r="M14" s="3" t="n"/>
+      <x:c r="N14" s="165"/>
+      <x:c r="O14" s="165"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="3" t="n"/>
@@ -5304,6 +5610,8 @@
       <x:c r="K15" s="15" t="n"/>
       <x:c r="L15" s="15" t="n"/>
       <x:c r="M15" s="3" t="n"/>
+      <x:c r="N15" s="165"/>
+      <x:c r="O15" s="165"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="3" t="n"/>
@@ -5319,6 +5627,8 @@
       <x:c r="K16" s="15" t="n"/>
       <x:c r="L16" s="15" t="n"/>
       <x:c r="M16" s="3" t="n"/>
+      <x:c r="N16" s="165"/>
+      <x:c r="O16" s="165"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="3" t="n"/>
@@ -5334,6 +5644,8 @@
       <x:c r="K17" s="15" t="n"/>
       <x:c r="L17" s="15" t="n"/>
       <x:c r="M17" s="3" t="n"/>
+      <x:c r="N17" s="165"/>
+      <x:c r="O17" s="165"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="3" t="n"/>
@@ -5349,6 +5661,8 @@
       <x:c r="K18" s="15" t="n"/>
       <x:c r="L18" s="15" t="n"/>
       <x:c r="M18" s="3" t="n"/>
+      <x:c r="N18" s="165"/>
+      <x:c r="O18" s="165"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="3" t="n"/>
@@ -5364,6 +5678,8 @@
       <x:c r="K19" s="15" t="n"/>
       <x:c r="L19" s="15" t="n"/>
       <x:c r="M19" s="3" t="n"/>
+      <x:c r="N19" s="165"/>
+      <x:c r="O19" s="165"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="3" t="n"/>
@@ -5379,6 +5695,8 @@
       <x:c r="K20" s="15" t="n"/>
       <x:c r="L20" s="15" t="n"/>
       <x:c r="M20" s="3" t="n"/>
+      <x:c r="N20" s="165"/>
+      <x:c r="O20" s="165"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="3" t="n"/>
@@ -5394,6 +5712,8 @@
       <x:c r="K21" s="15" t="n"/>
       <x:c r="L21" s="15" t="n"/>
       <x:c r="M21" s="3" t="n"/>
+      <x:c r="N21" s="165"/>
+      <x:c r="O21" s="165"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="3" t="n"/>
@@ -5409,6 +5729,8 @@
       <x:c r="K22" s="15" t="n"/>
       <x:c r="L22" s="15" t="n"/>
       <x:c r="M22" s="3" t="n"/>
+      <x:c r="N22" s="165"/>
+      <x:c r="O22" s="165"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="3" t="n"/>
@@ -5424,6 +5746,8 @@
       <x:c r="K23" s="15" t="n"/>
       <x:c r="L23" s="15" t="n"/>
       <x:c r="M23" s="3" t="n"/>
+      <x:c r="N23" s="165"/>
+      <x:c r="O23" s="165"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="3" t="n"/>
@@ -5439,6 +5763,8 @@
       <x:c r="K24" s="15" t="n"/>
       <x:c r="L24" s="15" t="n"/>
       <x:c r="M24" s="3" t="n"/>
+      <x:c r="N24" s="165"/>
+      <x:c r="O24" s="165"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5456,17 +5782,20 @@
       <x:formula>NOT(ISERROR(SEARCH("错误",M5)))</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A5:A24">
       <x:formula1>"building.player_home,building.residential_house,building.lumber_cabin,building.fishing_hut,building.farm_field,building.market,building.warehouse,building.road,building.tree"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="E5:E24">
       <x:formula1>"金币,泥土,石头,原木,木板,树苗,蔬菜,鱼,黄金鱼"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="N5:O24">
+      <x:formula1>"Default,Palace,PalaceImproved,PalaceAdvanced,PalaceRoyal,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47c67fd740844280"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87c656b1c5a0457d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5711,7 +6040,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc989b086244b48e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cf47e3c85c45fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6132,7 +6461,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd13291b301ab4c09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R941076eac91c4c24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6973,7 +7302,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54e4c221c49342bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5719590584054a3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8847,7 +9176,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf11167ad37334887"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5220b894caff4291"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9692,7 +10021,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a7f648a7def4fee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb6305daff8d438a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10956,6 +11285,188 @@
         <x:v>是</x:v>
       </x:c>
     </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="167" t="str">
+        <x:v>InventorySlotType</x:v>
+      </x:c>
+      <x:c r="B55" s="167" t="str">
+        <x:v>Default / Palace* / Warehouse* / ColdStorage / Cellar / Granary / Armory</x:v>
+      </x:c>
+      <x:c r="C55" s="167" t="str">
+        <x:v>建筑提供的库存格类型</x:v>
+      </x:c>
+      <x:c r="D55" s="167" t="str">
+        <x:v>InventorySlotType</x:v>
+      </x:c>
+      <x:c r="E55" s="167" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="167" t="str">
+        <x:v>等级_库存容量</x:v>
+      </x:c>
+      <x:c r="B56" s="167" t="str">
+        <x:v>槽位类型</x:v>
+      </x:c>
+      <x:c r="C56" s="167" t="str">
+        <x:v>王宫等通用库存提供模块的槽位类型</x:v>
+      </x:c>
+      <x:c r="D56" s="167" t="str">
+        <x:v>BuildingInventoryLevelConfiguration.SlotType</x:v>
+      </x:c>
+      <x:c r="E56" s="167" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="167" t="str">
+        <x:v>等级_仓库</x:v>
+      </x:c>
+      <x:c r="B57" s="167" t="str">
+        <x:v>基础槽位类型</x:v>
+      </x:c>
+      <x:c r="C57" s="167" t="str">
+        <x:v>仓库基础库存格的类型</x:v>
+      </x:c>
+      <x:c r="D57" s="167" t="str">
+        <x:v>WarehouseLevelConfiguration.BaseSlotType</x:v>
+      </x:c>
+      <x:c r="E57" s="167" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="167" t="str">
+        <x:v>等级_仓库</x:v>
+      </x:c>
+      <x:c r="B58" s="167" t="str">
+        <x:v>奖励槽位类型</x:v>
+      </x:c>
+      <x:c r="C58" s="167" t="str">
+        <x:v>达到奖励条件后新增库存格的类型</x:v>
+      </x:c>
+      <x:c r="D58" s="167" t="str">
+        <x:v>WarehouseLevelConfiguration.BonusSlotType</x:v>
+      </x:c>
+      <x:c r="E58" s="167" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="167" t="str">
+        <x:v>等级_住宅</x:v>
+      </x:c>
+      <x:c r="B59" s="167" t="str">
+        <x:v>FoodGroupId / 选择策略</x:v>
+      </x:c>
+      <x:c r="C59" s="167" t="str">
+        <x:v>居民可替代食物组和取用顺序</x:v>
+      </x:c>
+      <x:c r="D59" s="167" t="str">
+        <x:v>ResidentialHousingLevelConfiguration</x:v>
+      </x:c>
+      <x:c r="E59" s="167" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="167" t="str">
+        <x:v>库存边界</x:v>
+      </x:c>
+      <x:c r="B60" s="167" t="str">
+        <x:v>SlotType + Count</x:v>
+      </x:c>
+      <x:c r="C60" s="167" t="str">
+        <x:v>建筑不保存槽位固定损耗和 UI 表现</x:v>
+      </x:c>
+      <x:c r="D60" s="167" t="str">
+        <x:v>InventorySlotTypeCatalog / UI code</x:v>
+      </x:c>
+      <x:c r="E60" s="167" t="str">
+        <x:v>是</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="185" t="str">
+        <x:v>科技_全局库存Buff</x:v>
+      </x:c>
+      <x:c r="B61" s="185" t="str">
+        <x:v>BuffId</x:v>
+      </x:c>
+      <x:c r="C61" s="185" t="str">
+        <x:v>稳定全局 Buff ID</x:v>
+      </x:c>
+      <x:c r="D61" s="185" t="str">
+        <x:v>TechnologyGlobalBuffDefinition.BuffId</x:v>
+      </x:c>
+      <x:c r="E61" s="185" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F61" s="185" t="str">
+        <x:v>不得与其他科技全局 Buff 表重复</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="185" t="str">
+        <x:v>科技_全局库存Buff</x:v>
+      </x:c>
+      <x:c r="B62" s="185" t="str">
+        <x:v>ConditionId</x:v>
+      </x:c>
+      <x:c r="C62" s="185" t="str">
+        <x:v>激活科技条件</x:v>
+      </x:c>
+      <x:c r="D62" s="185" t="str">
+        <x:v>GameCondition_TechnologyUnlocked</x:v>
+      </x:c>
+      <x:c r="E62" s="185" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F62" s="185" t="str">
+        <x:v>格式 technology.&lt;TechnologyId&gt;</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="185" t="str">
+        <x:v>科技_全局库存Buff</x:v>
+      </x:c>
+      <x:c r="B63" s="185" t="str">
+        <x:v>库存损耗降低%</x:v>
+      </x:c>
+      <x:c r="C63" s="185" t="str">
+        <x:v>所有库存最终损耗率降低百分比</x:v>
+      </x:c>
+      <x:c r="D63" s="185" t="str">
+        <x:v>TechnologyGlobalBuffEffect_InventoryLossReduction</x:v>
+      </x:c>
+      <x:c r="E63" s="185" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F63" s="185" t="str">
+        <x:v>范围 (0,100]；多个 Buff 乘法叠加</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="185" t="str">
+        <x:v>科技_全局库存Buff</x:v>
+      </x:c>
+      <x:c r="B64" s="185" t="str">
+        <x:v>显示名</x:v>
+      </x:c>
+      <x:c r="C64" s="185" t="str">
+        <x:v>科技 UI 的 Buff 显示名</x:v>
+      </x:c>
+      <x:c r="D64" s="185" t="str">
+        <x:v>TechnologyGlobalBuffDefinition.DisplayName</x:v>
+      </x:c>
+      <x:c r="E64" s="185" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="F64" s="185" t="str">
+        <x:v>玩家可见</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A2:E2"/>
@@ -10963,7 +11474,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R137df4d56baa4ef0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d18ea22026c4354"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11186,7 +11697,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb8b49ee27134a66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9efeea724fe4203"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11829,6 +12340,210 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="169" t="str">
+        <x:v>科技全局 Buff：库存损耗</x:v>
+      </x:c>
+      <x:c r="B1" s="169"/>
+      <x:c r="C1" s="169"/>
+      <x:c r="D1" s="169"/>
+    </x:row>
+    <x:row r="2" ht="34" customHeight="1">
+      <x:c r="A2" s="172" t="str">
+        <x:v>由科技解锁条件激活，对所有库存槽位的最终损耗率统一乘算。多个全局库存损耗 Buff 使用乘法叠加。</x:v>
+      </x:c>
+      <x:c r="B2" s="172"/>
+      <x:c r="C2" s="172"/>
+      <x:c r="D2" s="172"/>
+    </x:row>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="177" t="str">
+        <x:v>BuffId</x:v>
+      </x:c>
+      <x:c r="B4" s="177" t="str">
+        <x:v>显示名</x:v>
+      </x:c>
+      <x:c r="C4" s="177" t="str">
+        <x:v>ConditionId</x:v>
+      </x:c>
+      <x:c r="D4" s="177" t="str">
+        <x:v>库存损耗降低%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="180" t="str">
+        <x:v>buff.inventory.wheel_preservation</x:v>
+      </x:c>
+      <x:c r="B5" s="180" t="str">
+        <x:v>轮子库存保存改良</x:v>
+      </x:c>
+      <x:c r="C5" s="180" t="str">
+        <x:v>technology.TN_4_5_轮子</x:v>
+      </x:c>
+      <x:c r="D5" s="181" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="D6" s="182"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="D7" s="182"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="D8" s="182"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="D9" s="182"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="D10" s="182"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="D11" s="182"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="D12" s="182"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="D13" s="182"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="D14" s="182"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="D15" s="182"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="D16" s="182"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="D17" s="182"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="D18" s="182"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="D19" s="182"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="D20" s="182"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="D21" s="182"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="D22" s="182"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="D23" s="182"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="D24" s="182"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="D25" s="182"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="D26" s="182"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="D27" s="182"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="D28" s="182"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="D29" s="182"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="D30" s="182"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="D31" s="182"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="D32" s="182"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="D33" s="182"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="D34" s="182"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="D35" s="182"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="D36" s="182"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="D37" s="182"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="D38" s="182"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="D39" s="182"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="D40" s="182"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="D41" s="182"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="D42" s="182"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="D43" s="182"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="D44" s="182"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="D45" s="182"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="D46" s="182"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="D47" s="182"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="D48" s="182"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="D49" s="182"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="D50" s="182"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="decimal" operator="between" sqref="D5:D50">
+      <x:formula1>0.01</x:formula1>
+      <x:formula2>100</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
@@ -12138,7 +12853,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00125ede0de94794"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2c571a3287b4088"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12519,7 +13234,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc97d3f7f0b1844e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69f48c83e69440ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13251,7 +13966,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87a8431e3f8941bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ba1d9fd7e8a421a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13526,7 +14241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R742ca9d4ac3f453e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd572f823a48420f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13770,7 +14485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5560bf36fcf34067"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20775b453ad349e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13783,6 +14498,7 @@
     <x:col min="2" max="2" width="9" style="42" customWidth="1"/>
     <x:col min="3" max="3" width="16" style="42" customWidth="1"/>
     <x:col min="4" max="4" width="18" style="42" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="42" customFormat="1" ht="30" customHeight="1">
@@ -13793,10 +14509,8 @@
       </x:c>
     </x:row>
     <x:row r="2" s="42" customFormat="1" ht="38" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">对应 BuildingInventoryLevelConfiguration；单位为库存格。</x:t>
-        </x:is>
+      <x:c r="A2" s="2" t="str">
+        <x:v>对应 BuildingInventoryLevelConfiguration；建筑只配置提供格数和槽位类型，库存规则由 InventorySlotTypeCatalog 解析。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -13826,6 +14540,9 @@
           <x:t xml:space="preserve">校验</x:t>
         </x:is>
       </x:c>
+      <x:c r="E4" s="163" t="str">
+        <x:v>槽位类型</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="inlineStr">
@@ -13843,6 +14560,9 @@
         <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A5,运营等级!$B$5:$B$24,B5)=0,"错误：缺少等级","通过")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
+      <x:c r="E5" s="165" t="str">
+        <x:v>Palace</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="inlineStr">
@@ -13860,6 +14580,9 @@
         <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A6,运营等级!$B$5:$B$24,B6)=0,"错误：缺少等级","通过")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
+      <x:c r="E6" s="165" t="str">
+        <x:v>PalaceImproved</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="inlineStr">
@@ -13877,6 +14600,9 @@
         <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A7,运营等级!$B$5:$B$24,B7)=0,"错误：缺少等级","通过")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
+      <x:c r="E7" s="165" t="str">
+        <x:v>PalaceAdvanced</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="inlineStr">
@@ -13889,6 +14615,272 @@
       </x:c>
       <x:c r="C8" s="13" t="n">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="e">
+        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A8,运营等级!$B$5:$B$24,B8)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>#NAME?</x:v>
+      </x:c>
+      <x:c r="E8" s="165" t="str">
+        <x:v>PalaceRoyal</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="3" t="n"/>
+      <x:c r="B9" s="15" t="n"/>
+      <x:c r="C9" s="15" t="n"/>
+      <x:c r="D9" s="3" t="n"/>
+      <x:c r="E9" s="165"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="3" t="n"/>
+      <x:c r="B10" s="15" t="n"/>
+      <x:c r="C10" s="15" t="n"/>
+      <x:c r="D10" s="3" t="n"/>
+      <x:c r="E10" s="165"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="3" t="n"/>
+      <x:c r="B11" s="15" t="n"/>
+      <x:c r="C11" s="15" t="n"/>
+      <x:c r="D11" s="3" t="n"/>
+      <x:c r="E11" s="165"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="3" t="n"/>
+      <x:c r="B12" s="15" t="n"/>
+      <x:c r="C12" s="15" t="n"/>
+      <x:c r="D12" s="3" t="n"/>
+      <x:c r="E12" s="165"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="3" t="n"/>
+      <x:c r="B13" s="15" t="n"/>
+      <x:c r="C13" s="15" t="n"/>
+      <x:c r="D13" s="3" t="n"/>
+      <x:c r="E13" s="165"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="n"/>
+      <x:c r="B14" s="15" t="n"/>
+      <x:c r="C14" s="15" t="n"/>
+      <x:c r="D14" s="3" t="n"/>
+      <x:c r="E14" s="165"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="n"/>
+      <x:c r="B15" s="15" t="n"/>
+      <x:c r="C15" s="15" t="n"/>
+      <x:c r="D15" s="3" t="n"/>
+      <x:c r="E15" s="165"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="n"/>
+      <x:c r="B16" s="15" t="n"/>
+      <x:c r="C16" s="15" t="n"/>
+      <x:c r="D16" s="3" t="n"/>
+      <x:c r="E16" s="165"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="3" t="n"/>
+      <x:c r="B17" s="15" t="n"/>
+      <x:c r="C17" s="15" t="n"/>
+      <x:c r="D17" s="3" t="n"/>
+      <x:c r="E17" s="165"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="n"/>
+      <x:c r="B18" s="15" t="n"/>
+      <x:c r="C18" s="15" t="n"/>
+      <x:c r="D18" s="3" t="n"/>
+      <x:c r="E18" s="165"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="n"/>
+      <x:c r="B19" s="15" t="n"/>
+      <x:c r="C19" s="15" t="n"/>
+      <x:c r="D19" s="3" t="n"/>
+      <x:c r="E19" s="165"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="3" t="n"/>
+      <x:c r="B20" s="15" t="n"/>
+      <x:c r="C20" s="15" t="n"/>
+      <x:c r="D20" s="3" t="n"/>
+      <x:c r="E20" s="165"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="3" t="n"/>
+      <x:c r="B21" s="15" t="n"/>
+      <x:c r="C21" s="15" t="n"/>
+      <x:c r="D21" s="3" t="n"/>
+      <x:c r="E21" s="165"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="3" t="n"/>
+      <x:c r="B22" s="15" t="n"/>
+      <x:c r="C22" s="15" t="n"/>
+      <x:c r="D22" s="3" t="n"/>
+      <x:c r="E22" s="165"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="3" t="n"/>
+      <x:c r="B23" s="15" t="n"/>
+      <x:c r="C23" s="15" t="n"/>
+      <x:c r="D23" s="3" t="n"/>
+      <x:c r="E23" s="165"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="3" t="n"/>
+      <x:c r="B24" s="15" t="n"/>
+      <x:c r="C24" s="15" t="n"/>
+      <x:c r="D24" s="3" t="n"/>
+      <x:c r="E24" s="165"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:D1"/>
+    <x:mergeCell ref="A2:D2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="D5:D8">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="between" text="通过">
+      <x:formula>NOT(ISERROR(SEARCH("通过",D5)))</x:formula>
+    </x:cfRule>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="between" text="待">
+      <x:formula>NOT(ISERROR(SEARCH("待",D5)))</x:formula>
+    </x:cfRule>
+    <x:cfRule type="containsText" dxfId="2" priority="3" operator="between" text="错误">
+      <x:formula>NOT(ISERROR(SEARCH("错误",D5)))</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A5:A24">
+      <x:formula1>"building.player_home,building.residential_house,building.lumber_cabin,building.fishing_hut,building.farm_field,building.market,building.warehouse,building.road,building.tree"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E24">
+      <x:formula1>"Default,Palace,PalaceImproved,PalaceAdvanced,PalaceRoyal,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff6c568e1e09470f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28" style="42" customWidth="1"/>
+    <x:col min="2" max="2" width="9" style="42" customWidth="1"/>
+    <x:col min="3" max="3" width="16" style="42" customWidth="1"/>
+    <x:col min="4" max="4" width="18" style="42" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" s="42" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">等级配置：科技点</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2" s="42" customFormat="1" ht="38" customHeight="1">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对应 BuildingTechnologyPointLevelConfiguration；每个成功回合注入当前研究。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="3" t="n"/>
+      <x:c r="B3" s="3" t="n"/>
+      <x:c r="C3" s="3" t="n"/>
+      <x:c r="D3" s="3" t="n"/>
+    </x:row>
+    <x:row r="4" s="42" customFormat="1" ht="30" customHeight="1">
+      <x:c r="A4" s="4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FamilyId</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Level</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">科技点/回合</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">校验</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">building.player_home</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="e">
+        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A5,运营等级!$B$5:$B$24,B5)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>#NAME?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">building.player_home</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="e">
+        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A6,运营等级!$B$5:$B$24,B6)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>#NAME?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">building.player_home</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="e">
+        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A7,运营等级!$B$5:$B$24,B7)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>#NAME?</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">building.player_home</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="13" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="14" t="e">
         <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A8,运营等级!$B$5:$B$24,B8)=0,"错误：缺少等级","通过")</x:f>
@@ -14014,251 +15006,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0143e6995eb2407b"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
-  <x:cols>
-    <x:col min="1" max="1" width="28" style="42" customWidth="1"/>
-    <x:col min="2" max="2" width="9" style="42" customWidth="1"/>
-    <x:col min="3" max="3" width="16" style="42" customWidth="1"/>
-    <x:col min="4" max="4" width="18" style="42" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" s="42" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">等级配置：科技点</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2" s="42" customFormat="1" ht="38" customHeight="1">
-      <x:c r="A2" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">对应 BuildingTechnologyPointLevelConfiguration；每个成功回合注入当前研究。</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="3" t="n"/>
-      <x:c r="B3" s="3" t="n"/>
-      <x:c r="C3" s="3" t="n"/>
-      <x:c r="D3" s="3" t="n"/>
-    </x:row>
-    <x:row r="4" s="42" customFormat="1" ht="30" customHeight="1">
-      <x:c r="A4" s="4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FamilyId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Level</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">科技点/回合</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">校验</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">building.player_home</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A5,运营等级!$B$5:$B$24,B5)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">building.player_home</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B6" s="13" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A6,运营等级!$B$5:$B$24,B6)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">building.player_home</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B7" s="13" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A7,运营等级!$B$5:$B$24,B7)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">building.player_home</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" s="13" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A8,运营等级!$B$5:$B$24,B8)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="3" t="n"/>
-      <x:c r="B9" s="15" t="n"/>
-      <x:c r="C9" s="15" t="n"/>
-      <x:c r="D9" s="3" t="n"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="3" t="n"/>
-      <x:c r="B10" s="15" t="n"/>
-      <x:c r="C10" s="15" t="n"/>
-      <x:c r="D10" s="3" t="n"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="3" t="n"/>
-      <x:c r="B11" s="15" t="n"/>
-      <x:c r="C11" s="15" t="n"/>
-      <x:c r="D11" s="3" t="n"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="3" t="n"/>
-      <x:c r="B12" s="15" t="n"/>
-      <x:c r="C12" s="15" t="n"/>
-      <x:c r="D12" s="3" t="n"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="3" t="n"/>
-      <x:c r="B13" s="15" t="n"/>
-      <x:c r="C13" s="15" t="n"/>
-      <x:c r="D13" s="3" t="n"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="3" t="n"/>
-      <x:c r="B14" s="15" t="n"/>
-      <x:c r="C14" s="15" t="n"/>
-      <x:c r="D14" s="3" t="n"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="3" t="n"/>
-      <x:c r="B15" s="15" t="n"/>
-      <x:c r="C15" s="15" t="n"/>
-      <x:c r="D15" s="3" t="n"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="3" t="n"/>
-      <x:c r="B16" s="15" t="n"/>
-      <x:c r="C16" s="15" t="n"/>
-      <x:c r="D16" s="3" t="n"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="3" t="n"/>
-      <x:c r="B17" s="15" t="n"/>
-      <x:c r="C17" s="15" t="n"/>
-      <x:c r="D17" s="3" t="n"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="3" t="n"/>
-      <x:c r="B18" s="15" t="n"/>
-      <x:c r="C18" s="15" t="n"/>
-      <x:c r="D18" s="3" t="n"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="3" t="n"/>
-      <x:c r="B19" s="15" t="n"/>
-      <x:c r="C19" s="15" t="n"/>
-      <x:c r="D19" s="3" t="n"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="3" t="n"/>
-      <x:c r="B20" s="15" t="n"/>
-      <x:c r="C20" s="15" t="n"/>
-      <x:c r="D20" s="3" t="n"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="3" t="n"/>
-      <x:c r="B21" s="15" t="n"/>
-      <x:c r="C21" s="15" t="n"/>
-      <x:c r="D21" s="3" t="n"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="3" t="n"/>
-      <x:c r="B22" s="15" t="n"/>
-      <x:c r="C22" s="15" t="n"/>
-      <x:c r="D22" s="3" t="n"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="3" t="n"/>
-      <x:c r="B23" s="15" t="n"/>
-      <x:c r="C23" s="15" t="n"/>
-      <x:c r="D23" s="3" t="n"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="3" t="n"/>
-      <x:c r="B24" s="15" t="n"/>
-      <x:c r="C24" s="15" t="n"/>
-      <x:c r="D24" s="3" t="n"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:D1"/>
-    <x:mergeCell ref="A2:D2"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="D5:D8">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="between" text="通过">
-      <x:formula>NOT(ISERROR(SEARCH("通过",D5)))</x:formula>
-    </x:cfRule>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="between" text="待">
-      <x:formula>NOT(ISERROR(SEARCH("待",D5)))</x:formula>
-    </x:cfRule>
-    <x:cfRule type="containsText" dxfId="2" priority="3" operator="between" text="错误">
-      <x:formula>NOT(ISERROR(SEARCH("错误",D5)))</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A5:A24">
-      <x:formula1>"building.player_home,building.residential_house,building.lumber_cabin,building.fishing_hut,building.farm_field,building.market,building.warehouse,building.road,building.tree"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72d2bb04d66c404e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c6a0591f6ed4379"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ConfigSource/Buildings/建筑数值策划表.xlsx
+++ b/ConfigSource/Buildings/建筑数值策划表.xlsx
@@ -2,35 +2,35 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rb4adb776360d4ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑家族" sheetId="2" r:id="Rc7871536722b48ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放置消耗" sheetId="3" r:id="R7214b6bef49049e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工消耗" sheetId="4" r:id="R9fb411d168494f6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营等级" sheetId="5" r:id="Ra6f97a1dc2084b84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级消耗" sheetId="6" r:id="Rca91b372040d4066"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_固定人口" sheetId="7" r:id="R1429843eae524a61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_库存容量" sheetId="8" r:id="R6a51c408e21d4e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_科技点" sheetId="9" r:id="Ra84d01f896ba4799"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_住宅" sheetId="10" r:id="R7afa443cff83447e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_岗位" sheetId="11" r:id="R9097a1e7c409491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_生产" sheetId="12" r:id="R5dd6d7e57ff04c97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_捕鱼稀有" sheetId="13" r:id="Rf30c877fc22741bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_仓库" sheetId="14" r:id="R8e9ce252264949a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_市场" sheetId="15" r:id="R0d802827293f4863"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_树木" sheetId="16" r:id="R5f47d26e37794698"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_范围效果" sheetId="17" r:id="Rba4bf5992c3249aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_作物" sheetId="18" r:id="Re63d5e45943d4800"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_种植消耗" sheetId="19" r:id="R51969da14f174e70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_收获产出" sheetId="20" r:id="R2da33eb1006944a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_自动收获" sheetId="21" r:id="Rd7ba4fef24cc4e61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视觉样式" sheetId="22" r:id="R548c4d1efb0e4614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="23" r:id="R83985afb69554fec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总检查" sheetId="24" r:id="R561f9a95dba3472e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工产出" sheetId="25" r:id="R5d35689fd8a94704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_维护费" sheetId="26" r:id="Re8124296c1934666"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局生产Buff" sheetId="27" r:id="R79745b744f8645cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_运营经验" sheetId="28" r:id="R2304328841334be5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局库存Buff" sheetId="29" r:id="Rbfeab2baf1974594"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R9d14b4c7432547b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="建筑家族" sheetId="2" r:id="Rd314a09b1c704d91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放置消耗" sheetId="3" r:id="R8396c5d65266497b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工消耗" sheetId="4" r:id="R7b95730a0c5e49c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营等级" sheetId="5" r:id="R6a33517b26784f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="升级消耗" sheetId="6" r:id="Ra2419905dd3b4625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_固定人口" sheetId="7" r:id="R890fdc79add64db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_库存容量" sheetId="8" r:id="Ra5ea085072014830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_科技点" sheetId="9" r:id="R3369e1518aac49e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_住宅" sheetId="10" r:id="R2df1759ba6f3446c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_岗位" sheetId="11" r:id="R34cb3af3fbd2463f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_生产" sheetId="12" r:id="R592799c953314ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_捕鱼稀有" sheetId="13" r:id="R24c32a30a3084734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_仓库" sheetId="14" r:id="Rd985047952d74ecb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_市场" sheetId="15" r:id="Rf3fa9ad296f544bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_树木" sheetId="16" r:id="Refc8d6827fa74d1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_范围效果" sheetId="17" r:id="R1b8f9387c0f4431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块_作物" sheetId="18" r:id="R5fdbfe9a36ea462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_种植消耗" sheetId="19" r:id="R46a63148396e4ad9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_收获产出" sheetId="20" r:id="Rf7350e99dcf64e1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作物_自动收获" sheetId="21" r:id="R4fc6ae070a344141"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="视觉样式" sheetId="22" r:id="R9856e67cbdb64dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据字典" sheetId="23" r:id="Rc7410fdc38a140c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总检查" sheetId="24" r:id="R3c38f0e7419649a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="施工产出" sheetId="25" r:id="R3d13e57f6bfa4c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_维护费" sheetId="26" r:id="R6be6be26b5984636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局生产Buff" sheetId="27" r:id="R41f5a3a52d614d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="等级_运营经验" sheetId="28" r:id="R93a67a2e8af5488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科技_全局库存Buff" sheetId="29" r:id="R8c04feee23c24861"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2282,7 +2282,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="29" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="3" t="n"/>
       <x:c r="D4" s="3" t="n"/>
@@ -2315,9 +2315,9 @@
           <x:t xml:space="preserve">当前家族数</x:t>
         </x:is>
       </x:c>
-      <x:c r="B6" s="29" t="e">
-        <x:f>COUNTA(建筑家族!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B6" s="29" t="n">
+        <x:f>COUNTA('建筑家族'!A5:A200)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="3" t="n"/>
       <x:c r="D6" s="3" t="n"/>
@@ -2332,9 +2332,9 @@
           <x:t xml:space="preserve">当前运营等级数</x:t>
         </x:is>
       </x:c>
-      <x:c r="B7" s="29" t="e">
-        <x:f>COUNTA(运营等级!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B7" s="29" t="n">
+        <x:f>COUNTA('运营等级'!A5:A200)</x:f>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="3" t="n"/>
       <x:c r="D7" s="3" t="n"/>
@@ -3224,7 +3224,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7864dc9d7ed48b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f846bac2903431e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3969,28 +3969,103 @@
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="3" t="n"/>
-      <x:c r="B23" s="15" t="n"/>
-      <x:c r="C23" s="15" t="n"/>
-      <x:c r="D23" s="15" t="n"/>
-      <x:c r="E23" s="15" t="n"/>
-      <x:c r="F23" s="15" t="n"/>
-      <x:c r="G23" s="3" t="n"/>
-      <x:c r="H23" s="15" t="n"/>
-      <x:c r="I23" s="3" t="n"/>
-      <x:c r="J23" s="3" t="n"/>
+      <x:c r="A23" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G23" s="3" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="H23" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="3" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:f>IF(OR(D23&gt;C23,H23&gt;C23),"错误：工人超上限","通过")</x:f>
+        <x:v>通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="3" t="n"/>
-      <x:c r="B24" s="15" t="n"/>
-      <x:c r="C24" s="15" t="n"/>
-      <x:c r="D24" s="15" t="n"/>
-      <x:c r="E24" s="15" t="n"/>
-      <x:c r="F24" s="15" t="n"/>
-      <x:c r="G24" s="3" t="n"/>
-      <x:c r="H24" s="15" t="n"/>
-      <x:c r="I24" s="3" t="n"/>
-      <x:c r="J24" s="3" t="n"/>
+      <x:c r="A24" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B24" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G24" s="3" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="H24" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="3" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:f>IF(OR(D24&gt;C24,H24&gt;C24),"错误：工人超上限","通过")</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:f>IF(OR(D25&gt;C25,H25&gt;C25),"错误：工人超上限","通过")</x:f>
+        <x:v>通过</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -4021,7 +4096,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb24d3efd470548c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R156e87f973944a33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4133,9 +4208,9 @@
         <x:f>E5/F5</x:f>
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="H5" s="10" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A5,等级_岗位!$B$5:$B$24,B5)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H5" s="10" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A5,'等级_岗位'!$B$5:$B$200,B5)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -4165,9 +4240,9 @@
         <x:f>E6/F6</x:f>
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="H6" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A6,等级_岗位!$B$5:$B$24,B6)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H6" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A6,'等级_岗位'!$B$5:$B$200,B6)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4197,9 +4272,9 @@
         <x:f>E7/F7</x:f>
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A7,等级_岗位!$B$5:$B$24,B7)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H7" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A7,'等级_岗位'!$B$5:$B$200,B7)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4229,9 +4304,9 @@
         <x:f>E8/F8</x:f>
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="H8" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A8,等级_岗位!$B$5:$B$24,B8)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H8" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A8,'等级_岗位'!$B$5:$B$200,B8)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4261,9 +4336,9 @@
         <x:f>E9/F9</x:f>
         <x:v>1.3333333333333333</x:v>
       </x:c>
-      <x:c r="H9" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A9,等级_岗位!$B$5:$B$24,B9)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H9" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A9,'等级_岗位'!$B$5:$B$200,B9)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -4293,9 +4368,9 @@
         <x:f>E10/F10</x:f>
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="H10" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A10,等级_岗位!$B$5:$B$24,B10)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H10" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A10,'等级_岗位'!$B$5:$B$200,B10)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -4325,9 +4400,9 @@
         <x:f>E11/F11</x:f>
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="H11" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A11,等级_岗位!$B$5:$B$24,B11)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H11" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A11,'等级_岗位'!$B$5:$B$200,B11)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4357,9 +4432,9 @@
         <x:f>E12/F12</x:f>
         <x:v>0.3333333333333333</x:v>
       </x:c>
-      <x:c r="H12" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A12,等级_岗位!$B$5:$B$24,B12)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H12" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A12,'等级_岗位'!$B$5:$B$200,B12)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4389,9 +4464,9 @@
         <x:f>E13/F13</x:f>
         <x:v>0.6666666666666666</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A13,等级_岗位!$B$5:$B$24,B13)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H13" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A13,'等级_岗位'!$B$5:$B$200,B13)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4417,9 +4492,9 @@
         <x:f>E14/F14</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A14,等级_岗位!$B$5:$B$24,B14)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H14" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A14,'等级_岗位'!$B$5:$B$200,B14)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4445,9 +4520,9 @@
         <x:f>E15/F15</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A15,等级_岗位!$B$5:$B$24,B15)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H15" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A15,'等级_岗位'!$B$5:$B$200,B15)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4473,9 +4548,9 @@
         <x:f>E16/F16</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H16" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A16,等级_岗位!$B$5:$B$24,B16)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H16" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A16,'等级_岗位'!$B$5:$B$200,B16)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4501,9 +4576,9 @@
         <x:f>E17/F17</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A17,等级_岗位!$B$5:$B$24,B17)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H17" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A17,'等级_岗位'!$B$5:$B$200,B17)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4529,9 +4604,9 @@
         <x:f>E18/F18</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H18" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A18,等级_岗位!$B$5:$B$24,B18)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H18" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A18,'等级_岗位'!$B$5:$B$200,B18)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4557,9 +4632,9 @@
         <x:f>E19/F19</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H19" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A19,等级_岗位!$B$5:$B$24,B19)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H19" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A19,'等级_岗位'!$B$5:$B$200,B19)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -4585,9 +4660,9 @@
         <x:f>E20/F20</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H20" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A20,等级_岗位!$B$5:$B$24,B20)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H20" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A20,'等级_岗位'!$B$5:$B$200,B20)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4613,9 +4688,9 @@
         <x:f>E21/F21</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H21" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A21,等级_岗位!$B$5:$B$24,B21)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H21" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A21,'等级_岗位'!$B$5:$B$200,B21)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4641,9 +4716,9 @@
         <x:f>E22/F22</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A22,等级_岗位!$B$5:$B$24,B22)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H22" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A22,'等级_岗位'!$B$5:$B$200,B22)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4669,9 +4744,9 @@
         <x:f>E23/F23</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H23" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A23,等级_岗位!$B$5:$B$24,B23)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H23" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A23,'等级_岗位'!$B$5:$B$200,B23)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4697,9 +4772,9 @@
         <x:f>E24/F24</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A24,等级_岗位!$B$5:$B$24,B24)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H24" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A24,'等级_岗位'!$B$5:$B$200,B24)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -4725,9 +4800,9 @@
         <x:f>E25/F25</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H25" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A25,等级_岗位!$B$5:$B$24,B25)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H25" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A25,'等级_岗位'!$B$5:$B$200,B25)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -4753,9 +4828,9 @@
         <x:f>E26/F26</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H26" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A26,等级_岗位!$B$5:$B$24,B26)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H26" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A26,'等级_岗位'!$B$5:$B$200,B26)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -4781,9 +4856,9 @@
         <x:f>E27/F27</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H27" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A27,等级_岗位!$B$5:$B$24,B27)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H27" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A27,'等级_岗位'!$B$5:$B$200,B27)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -4809,9 +4884,9 @@
         <x:f>E28/F28</x:f>
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H28" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A28,等级_岗位!$B$5:$B$24,B28)=0,"错误：缺少岗位","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="H28" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A28,'等级_岗位'!$B$5:$B$200,B28)=0,"错误：缺少岗位","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4840,7 +4915,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc3f89b25b5d4462"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d462854600a4a71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5199,7 +5274,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25e95b44002d47e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc779de2e47eb48ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5362,15 +5437,15 @@
       <x:c r="L5" s="9" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="M5" s="10" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A5,等级_岗位!$B$5:$B$24,B5)=0,"错误：缺少岗位",IF(MAX(C5,G5,J5)&gt;SUMIFS(等级_岗位!$C$5:$C$24,等级_岗位!$A$5:$A$24,A5,等级_岗位!$B$5:$B$24,B5),"错误：阈值超上限","通过"))</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="M5" s="10" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A5,'等级_岗位'!$B$5:$B$200,B5)=0,"错误：缺少岗位",IF(MAX(C5,G5,J5)&gt;SUMIFS('等级_岗位'!$C$5:$C$200,'等级_岗位'!$A$5:$A$200,A5,'等级_岗位'!$B$5:$B$200,B5),"错误：阈值超上限","通过"))</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="N5" s="165" t="str">
-        <x:v>BasicWarehouse</x:v>
+        <x:v>简陋库存</x:v>
       </x:c>
       <x:c r="O5" s="165" t="str">
-        <x:v>BasicWarehouse</x:v>
+        <x:v>简陋库存</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5414,15 +5489,15 @@
       <x:c r="L6" s="13" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="M6" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A6,等级_岗位!$B$5:$B$24,B6)=0,"错误：缺少岗位",IF(MAX(C6,G6,J6)&gt;SUMIFS(等级_岗位!$C$5:$C$24,等级_岗位!$A$5:$A$24,A6,等级_岗位!$B$5:$B$24,B6),"错误：阈值超上限","通过"))</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="M6" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A6,'等级_岗位'!$B$5:$B$200,B6)=0,"错误：缺少岗位",IF(MAX(C6,G6,J6)&gt;SUMIFS('等级_岗位'!$C$5:$C$200,'等级_岗位'!$A$5:$A$200,A6,'等级_岗位'!$B$5:$B$200,B6),"错误：阈值超上限","通过"))</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="N6" s="165" t="str">
-        <x:v>Warehouse</x:v>
+        <x:v>普通库存</x:v>
       </x:c>
       <x:c r="O6" s="165" t="str">
-        <x:v>Warehouse</x:v>
+        <x:v>普通库存</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5466,67 +5541,160 @@
       <x:c r="L7" s="13" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="e">
-        <x:f>IF(COUNTIFS(等级_岗位!$A$5:$A$24,A7,等级_岗位!$B$5:$B$24,B7)=0,"错误：缺少岗位",IF(MAX(C7,G7,J7)&gt;SUMIFS(等级_岗位!$C$5:$C$24,等级_岗位!$A$5:$A$24,A7,等级_岗位!$B$5:$B$24,B7),"错误：阈值超上限","通过"))</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="M7" s="14" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A7,'等级_岗位'!$B$5:$B$200,B7)=0,"错误：缺少岗位",IF(MAX(C7,G7,J7)&gt;SUMIFS('等级_岗位'!$C$5:$C$200,'等级_岗位'!$A$5:$A$200,A7,'等级_岗位'!$B$5:$B$200,B7),"错误：阈值超上限","通过"))</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="N7" s="165" t="str">
-        <x:v>AdvancedWarehouse</x:v>
+        <x:v>高级库存</x:v>
       </x:c>
       <x:c r="O7" s="165" t="str">
-        <x:v>AdvancedWarehouse</x:v>
+        <x:v>高级库存</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="3" t="n"/>
-      <x:c r="B8" s="15" t="n"/>
-      <x:c r="C8" s="15" t="n"/>
-      <x:c r="D8" s="15" t="n"/>
-      <x:c r="E8" s="15" t="n"/>
-      <x:c r="F8" s="15" t="n"/>
-      <x:c r="G8" s="15" t="n"/>
-      <x:c r="H8" s="15" t="n"/>
-      <x:c r="I8" s="15" t="n"/>
-      <x:c r="J8" s="15" t="n"/>
-      <x:c r="K8" s="15" t="n"/>
-      <x:c r="L8" s="15" t="n"/>
-      <x:c r="M8" s="3" t="n"/>
-      <x:c r="N8" s="165"/>
-      <x:c r="O8" s="165"/>
+      <x:c r="A8" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A8,'等级_岗位'!$B$5:$B$200,B8)=0,"错误：缺少岗位",IF(MAX(C8,G8,J8)&gt;SUMIFS('等级_岗位'!$C$5:$C$200,'等级_岗位'!$A$5:$A$200,A8,'等级_岗位'!$B$5:$B$200,B8),"错误：阈值超上限","通过"))</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="N8" s="165" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
+      <x:c r="O8" s="165" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="3" t="n"/>
-      <x:c r="B9" s="15" t="n"/>
-      <x:c r="C9" s="15" t="n"/>
-      <x:c r="D9" s="15" t="n"/>
-      <x:c r="E9" s="15" t="n"/>
-      <x:c r="F9" s="15" t="n"/>
-      <x:c r="G9" s="15" t="n"/>
-      <x:c r="H9" s="15" t="n"/>
-      <x:c r="I9" s="15" t="n"/>
-      <x:c r="J9" s="15" t="n"/>
-      <x:c r="K9" s="15" t="n"/>
-      <x:c r="L9" s="15" t="n"/>
-      <x:c r="M9" s="3" t="n"/>
-      <x:c r="N9" s="165"/>
-      <x:c r="O9" s="165"/>
+      <x:c r="A9" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H9" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A9,'等级_岗位'!$B$5:$B$200,B9)=0,"错误：缺少岗位",IF(MAX(C9,G9,J9)&gt;SUMIFS('等级_岗位'!$C$5:$C$200,'等级_岗位'!$A$5:$A$200,A9,'等级_岗位'!$B$5:$B$200,B9),"错误：阈值超上限","通过"))</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="N9" s="165" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
+      <x:c r="O9" s="165" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="3" t="n"/>
-      <x:c r="B10" s="15" t="n"/>
-      <x:c r="C10" s="15" t="n"/>
-      <x:c r="D10" s="15" t="n"/>
-      <x:c r="E10" s="15" t="n"/>
-      <x:c r="F10" s="15" t="n"/>
-      <x:c r="G10" s="15" t="n"/>
-      <x:c r="H10" s="15" t="n"/>
-      <x:c r="I10" s="15" t="n"/>
-      <x:c r="J10" s="15" t="n"/>
-      <x:c r="K10" s="15" t="n"/>
-      <x:c r="L10" s="15" t="n"/>
-      <x:c r="M10" s="3" t="n"/>
-      <x:c r="N10" s="165"/>
-      <x:c r="O10" s="165"/>
+      <x:c r="A10" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K10" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L10" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="M10" s="3" t="str">
+        <x:f>IF(COUNTIFS('等级_岗位'!$A$5:$A$200,A10,'等级_岗位'!$B$5:$B$200,B10)=0,"错误：缺少岗位",IF(MAX(C10,G10,J10)&gt;SUMIFS('等级_岗位'!$C$5:$C$200,'等级_岗位'!$A$5:$A$200,A10,'等级_岗位'!$B$5:$B$200,B10),"错误：阈值超上限","通过"))</x:f>
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="N10" s="165" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
+      <x:c r="O10" s="165" t="str">
+        <x:v>粮库</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="n"/>
@@ -5782,7 +5950,7 @@
       <x:formula>NOT(ISERROR(SEARCH("错误",M5)))</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A5:A24">
       <x:formula1>"building.player_home,building.residential_house,building.lumber_cabin,building.fishing_hut,building.farm_field,building.market,building.warehouse,building.road,building.tree"</x:formula1>
     </x:dataValidation>
@@ -5792,10 +5960,13 @@
     <x:dataValidation type="list" sqref="N5:O24">
       <x:formula1>"Default,Palace,PalaceImproved,PalaceAdvanced,PalaceRoyal,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="N5:O204">
+      <x:formula1>"简陋库存,普通库存,高级库存,冻库,粮库"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87c656b1c5a0457d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d8499e6c2794600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6040,7 +6211,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cf47e3c85c45fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58fd51e535fd430b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6461,7 +6632,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R941076eac91c4c24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R447be15506f047ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7302,7 +7473,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5719590584054a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re542e71cf4274ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8937,27 +9108,67 @@
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="3" t="n"/>
-      <x:c r="B18" s="3" t="n"/>
-      <x:c r="C18" s="3" t="n"/>
-      <x:c r="D18" s="15" t="n"/>
-      <x:c r="E18" s="15" t="n"/>
-      <x:c r="F18" s="3" t="n"/>
-      <x:c r="G18" s="3" t="n"/>
-      <x:c r="H18" s="15" t="n"/>
-      <x:c r="I18" s="15" t="n"/>
-      <x:c r="J18" s="15" t="n"/>
-      <x:c r="K18" s="3" t="n"/>
-      <x:c r="L18" s="3" t="n"/>
-      <x:c r="M18" s="3" t="n"/>
-      <x:c r="N18" s="15" t="n"/>
-      <x:c r="O18" s="3" t="n"/>
-      <x:c r="P18" s="3" t="n"/>
-      <x:c r="Q18" s="15" t="n"/>
-      <x:c r="R18" s="15" t="n"/>
-      <x:c r="S18" s="3" t="n"/>
+      <x:c r="A18" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str">
+        <x:v>粮仓</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>农业</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F18" s="3" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="G18" s="3" t="str">
+        <x:v>陆地</x:v>
+      </x:c>
+      <x:c r="H18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="N18" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="Q18" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="15" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="str">
+        <x:v>农业解锁蓝图；岗位、维护费、经验与粮库槽位见等级_仓库</x:v>
+      </x:c>
       <x:c r="T18" s="100"/>
-      <x:c r="U18" s="100"/>
+      <x:c r="U18" s="100" t="str">
+        <x:v>technology.TN_2_2_农业</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="3" t="n"/>
@@ -9176,7 +9387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5220b894caff4291"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90e1af31af774489"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10021,7 +10232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb6305daff8d438a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2ae9edf63644b90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11290,7 +11501,7 @@
         <x:v>InventorySlotType</x:v>
       </x:c>
       <x:c r="B55" s="167" t="str">
-        <x:v>Default / Palace* / Warehouse* / ColdStorage / Cellar / Granary / Armory</x:v>
+        <x:v>简陋库存 / 普通库存 / 高级库存 / 冻库 / 粮库</x:v>
       </x:c>
       <x:c r="C55" s="167" t="str">
         <x:v>建筑提供的库存格类型</x:v>
@@ -11474,7 +11685,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d18ea22026c4354"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R506fafd3cbac4f01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11531,35 +11742,35 @@
       <x:c r="A5" s="7" t="str">
         <x:v>家族数量</x:v>
       </x:c>
-      <x:c r="B5" s="8" t="e">
-        <x:f>COUNTA(建筑家族!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B5" s="8" t="n">
+        <x:f>COUNTA('建筑家族'!A5:A200)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="9" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="e">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D5" s="10" t="str">
         <x:f>IF(B5=C5,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E5" s="7" t="str">
-        <x:v>当前项目正式家族（含医院与警局）</x:v>
+        <x:v>当前项目正式家族（含粮仓）</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
         <x:v>运营等级数量</x:v>
       </x:c>
-      <x:c r="B6" s="12" t="e">
-        <x:f>COUNTA(运营等级!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B6" s="12" t="n">
+        <x:f>COUNTA('运营等级'!A5:A200)</x:f>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="13" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="e">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
         <x:f>IF(B6=C6,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
         <x:v>含未开放占位等级</x:v>
@@ -11569,16 +11780,16 @@
       <x:c r="A7" s="11" t="str">
         <x:v>生产档位行数</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="e">
-        <x:f>COUNTA(等级_生产!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B7" s="12" t="n">
+        <x:f>COUNTA('等级_生产'!A5:A200)</x:f>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="13" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="e">
+      <x:c r="D7" s="14" t="str">
         <x:f>IF(B7=C7,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
         <x:v>保持当前生产档位完整</x:v>
@@ -11588,16 +11799,16 @@
       <x:c r="A8" s="11" t="str">
         <x:v>范围效果行数</x:v>
       </x:c>
-      <x:c r="B8" s="12" t="e">
-        <x:f>COUNTA(模块_范围效果!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B8" s="12" t="n">
+        <x:f>COUNTA('模块_范围效果'!A5:A200)</x:f>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="13" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="e">
+      <x:c r="D8" s="14" t="str">
         <x:f>IF(B8=C8,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
         <x:v>树木、雕塑、医院六档医疗与警局六档治安</x:v>
@@ -11607,35 +11818,35 @@
       <x:c r="A9" s="11" t="str">
         <x:v>仓库等级行数</x:v>
       </x:c>
-      <x:c r="B9" s="12" t="e">
-        <x:f>COUNTA(等级_仓库!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B9" s="12" t="n">
+        <x:f>COUNTA('等级_仓库'!A5:A200)</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="13" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="e">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="str">
         <x:f>IF(B9=C9,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>LV1-LV3 均有仓库运营配置</x:v>
+        <x:v>仓库与粮仓的 LV1-LV3 均有仓库运营配置</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
         <x:v>运营经验等级行数</x:v>
       </x:c>
-      <x:c r="B10" s="12" t="e">
-        <x:f>COUNTA(等级_运营经验!A5:A200)</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B10" s="12" t="n">
+        <x:f>COUNTA('等级_运营经验'!A5:A200)</x:f>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="13" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="e">
+      <x:c r="D10" s="14" t="str">
         <x:f>IF(B10=C10,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
         <x:v>医院与警局的 LV1-LV3 均有通用经验配置</x:v>
@@ -11645,16 +11856,16 @@
       <x:c r="A11" s="11" t="str">
         <x:v>Style 待回填数</x:v>
       </x:c>
-      <x:c r="B11" s="12" t="e">
-        <x:f>COUNTIF(视觉样式!F5:F200,"待回填")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B11" s="12" t="n">
+        <x:f>COUNTIF('视觉样式'!F5:F200,"待回填")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="13" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="e">
+      <x:c r="D11" s="14" t="str">
         <x:f>IF(B11=C11,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
         <x:v>美术回填不阻止数值导入</x:v>
@@ -11664,19 +11875,19 @@
       <x:c r="A12" t="str">
         <x:v>SchemaVersion</x:v>
       </x:c>
-      <x:c r="B12" t="e">
-        <x:f>说明!B4</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="B12" t="n">
+        <x:f>'说明'!B4</x:f>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C12" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" t="e">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
         <x:f>IF(B12=C12,"通过","待检查")</x:f>
-        <x:v>#NAME?</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>通用运营经验与条件化医疗/治安范围效果</x:v>
+        <x:v>当前正式建筑数值 SchemaVersion</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11697,7 +11908,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9efeea724fe4203"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb51af65eb4a04d7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12779,10 +12990,18 @@
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="3" t="n"/>
-      <x:c r="B15" s="3" t="n"/>
-      <x:c r="C15" s="15" t="n"/>
-      <x:c r="D15" s="3" t="n"/>
+      <x:c r="A15" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>金币</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>确认放置时支付</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="3" t="n"/>
@@ -12853,7 +13072,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2c571a3287b4088"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R94e573df393548cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13164,25 +13383,55 @@
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="3" t="n"/>
-      <x:c r="B17" s="15" t="n"/>
-      <x:c r="C17" s="15" t="n"/>
-      <x:c r="D17" s="15" t="n"/>
-      <x:c r="E17" s="3" t="n"/>
+      <x:c r="A17" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="str">
+        <x:v>泥土</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="3" t="str">
+        <x:v>第 1 施工阶段（粘土资产的稳定 ItemId 为泥土）</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="3" t="n"/>
-      <x:c r="B18" s="15" t="n"/>
-      <x:c r="C18" s="15" t="n"/>
-      <x:c r="D18" s="15" t="n"/>
-      <x:c r="E18" s="3" t="n"/>
+      <x:c r="A18" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="str">
+        <x:v>原木</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="str">
+        <x:v>第 2 施工阶段（木材映射为基础资源原木）</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="3" t="n"/>
-      <x:c r="B19" s="15" t="n"/>
-      <x:c r="C19" s="15" t="n"/>
-      <x:c r="D19" s="15" t="n"/>
-      <x:c r="E19" s="3" t="n"/>
+      <x:c r="A19" s="3" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="str">
+        <x:v>石头</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E19" s="3" t="str">
+        <x:v>第 3 施工阶段</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="3" t="n"/>
@@ -13234,7 +13483,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69f48c83e69440ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f53061be0064536"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13951,6 +14200,57 @@
         <x:v>信息化解锁；最高等级</x:v>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>施工完成进入 LV1；累计 30 EXP 后可升 LV2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B35" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>无额外科技条件；累计 50 EXP 后可升 LV3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>building.granary</x:v>
+      </x:c>
+      <x:c r="B36" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>最高等级；5 工人永久额外提供 1 个粮库槽</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A2:E2"/>
@@ -13966,7 +14266,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ba1d9fd7e8a421a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95f3eb4864244151"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14241,7 +14541,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd572f823a48420f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcafafa87d55d4b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14310,9 +14610,9 @@
       <x:c r="C5" s="9" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A5,运营等级!$B$5:$B$24,B5)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D5" s="10" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A5,'运营等级'!$B$5:$B$200,B5)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -14327,9 +14627,9 @@
       <x:c r="C6" s="13" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A6,运营等级!$B$5:$B$24,B6)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D6" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A6,'运营等级'!$B$5:$B$200,B6)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -14344,9 +14644,9 @@
       <x:c r="C7" s="13" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A7,运营等级!$B$5:$B$24,B7)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D7" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A7,'运营等级'!$B$5:$B$200,B7)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -14361,9 +14661,9 @@
       <x:c r="C8" s="13" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A8,运营等级!$B$5:$B$24,B8)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D8" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A8,'运营等级'!$B$5:$B$200,B8)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -14485,7 +14785,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20775b453ad349e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66dff0044803401c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14556,12 +14856,12 @@
       <x:c r="C5" s="9" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A5,运营等级!$B$5:$B$24,B5)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D5" s="10" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A5,'运营等级'!$B$5:$B$200,B5)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E5" s="165" t="str">
-        <x:v>Palace</x:v>
+        <x:v>简陋库存</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -14576,12 +14876,12 @@
       <x:c r="C6" s="13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A6,运营等级!$B$5:$B$24,B6)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D6" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A6,'运营等级'!$B$5:$B$200,B6)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E6" s="165" t="str">
-        <x:v>PalaceImproved</x:v>
+        <x:v>普通库存</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -14596,12 +14896,12 @@
       <x:c r="C7" s="13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A7,运营等级!$B$5:$B$24,B7)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D7" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A7,'运营等级'!$B$5:$B$200,B7)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E7" s="165" t="str">
-        <x:v>PalaceAdvanced</x:v>
+        <x:v>高级库存</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -14616,12 +14916,12 @@
       <x:c r="C8" s="13" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A8,运营等级!$B$5:$B$24,B8)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D8" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A8,'运营等级'!$B$5:$B$200,B8)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E8" s="165" t="str">
-        <x:v>PalaceRoyal</x:v>
+        <x:v>高级库存</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -14752,17 +15052,20 @@
       <x:formula>NOT(ISERROR(SEARCH("错误",D5)))</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" sqref="A5:A24">
       <x:formula1>"building.player_home,building.residential_house,building.lumber_cabin,building.fishing_hut,building.farm_field,building.market,building.warehouse,building.road,building.tree"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E5:E24">
       <x:formula1>"Default,Palace,PalaceImproved,PalaceAdvanced,PalaceRoyal,BasicWarehouse,Warehouse,AdvancedWarehouse,ColdStorage,Cellar,Granary,Armory"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="E5:E204">
+      <x:formula1>"简陋库存,普通库存,高级库存,冻库,粮库"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff6c568e1e09470f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ead207e29494b1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14831,9 +15134,9 @@
       <x:c r="C5" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="10" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A5,运营等级!$B$5:$B$24,B5)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D5" s="10" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A5,'运营等级'!$B$5:$B$200,B5)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -14848,9 +15151,9 @@
       <x:c r="C6" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D6" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A6,运营等级!$B$5:$B$24,B6)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D6" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A6,'运营等级'!$B$5:$B$200,B6)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -14865,9 +15168,9 @@
       <x:c r="C7" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A7,运营等级!$B$5:$B$24,B7)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D7" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A7,'运营等级'!$B$5:$B$200,B7)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -14882,9 +15185,9 @@
       <x:c r="C8" s="13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="e">
-        <x:f>IF(COUNTIFS(运营等级!$A$5:$A$24,A8,运营等级!$B$5:$B$24,B8)=0,"错误：缺少等级","通过")</x:f>
-        <x:v>#NAME?</x:v>
+      <x:c r="D8" s="14" t="str">
+        <x:f>IF(COUNTIFS('运营等级'!$A$5:$A$200,A8,'运营等级'!$B$5:$B$200,B8)=0,"错误：缺少等级","通过")</x:f>
+        <x:v>通过</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -15006,7 +15309,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c6a0591f6ed4379"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re43f2d463990488d"/>
   </x:tableParts>
 </x:worksheet>
 </file>